--- a/research_AT.xlsx
+++ b/research_AT.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -837,6 +837,102 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>pan-EU</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>excl. VAT (net price shown; site computes gross at 19%, e.g. 46.99 net / 55.92 gross)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Free delivery ('Kostenloser Versand'; site states prices incl. delivery)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>not shown; smallwares mostly sold in sets of 6, 8 or 12</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>German pan-EU gastro supplier (GGM Gastro International). Prices appear via JavaScript on screen, but each product page's HTML carries schema.org price data for the de-at storefront (net and gross); those values were recorded. Product URLs found via GGM's public sitemap. B2B only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>excl. VAT ('Zzgl. 20% MwSt.'; gross incl. 20% also shown)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Austria: free delivery ('frei Haus') from 300 EUR net goods value; charges below that not stated on the shipping page</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>not shown</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Austrian B2B gastro equipment shop (WooCommerce). BELOW the 6-item threshold (5 items: plastic GN items from HENDI/RIEBER and Rieber front loaders only; no squeeze bottles, boards, dough boxes or trays in its catalogue). Included at the user's request; prices are counted in the Summary.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -848,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -950,26 +1046,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Schneider Polycarbonat GN 1/1 Behälter 65 mm, 8,5 l</t>
+          <t>(6 Stück) Polycarbonat-Behälter GN 1/1 - Transparent - Höhe: 65mm</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneider-polycarbonat-gn-11-behaelter-65-mm-85-l-530100</t>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-polycarbonat-behaelter-gn-1-1-transparent-hoehe-65mm-gpcp1165</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>20.69</v>
+        <v>46.99</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -977,11 +1073,15 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="n">
-        <v>20.69</v>
+        <v>7.83</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -990,7 +1090,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Sale price (normal 21.39); minimum order quantity 4 pcs</t>
+          <t>RRP 87.99</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -1010,26 +1110,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>Gastro Star</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hendi Gastronorm-Behälter 1/1, GN 1/1, 9L, Transparent, 530x325x(H)65mm – Polycarbonat</t>
+          <t>RIEBER GN 1/1 Polycarbonat-Behälter - Tiefe 65mm</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Rieber</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-polykarbonat-transparent-gn-1-1-9-l-530-x-325-x-h-65-mm</t>
+          <t>https://www.gastro-star.at/produkt/riebergn11polycarbonat-behaelter-tiefe65mm/</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>22.43</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -1041,14 +1141,18 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>22.43</v>
+        <v>23</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Gross 27.60</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1066,30 +1170,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Vogue Polycarbonat GN-Behälter GN1/1 65mm</t>
+          <t>Schneider Polycarbonat GN 1/1 Behälter 65 mm, 8,5 l</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/3020@GN-U224/Vogue-Polycarbonat-GN-Beh%C3%A4lter-GN1-1-65mm.htm</t>
+          <t>https://www.gastro-hero.at/products/schneider-polycarbonat-gn-11-behaelter-65-mm-85-l-530100</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.49</v>
+        <v>20.69</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -1097,7 +1201,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>10.41</v>
+        <v>20.69</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -1106,7 +1210,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Currently 'zurzeit nicht am Lager' (out of stock)</t>
+          <t>Sale price (normal 21.39); minimum order quantity 4 pcs</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1126,26 +1230,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Gastronormbehälter GN 1/1 x 65 mm GN 94 Polycarbonat transparent</t>
+          <t>Hendi Gastronorm-Behälter 1/1, GN 1/1, 9L, Transparent, 530x325x(H)65mm – Polycarbonat</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/gastronormbehaelter-gn-1-1-x-65-mm-gn-94-polycarbonat-transparent-252042</t>
+          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-polykarbonat-transparent-gn-1-1-9-l-530-x-325-x-h-65-mm</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>14.07</v>
+        <v>22.43</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -1157,18 +1261,14 @@
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>14.07</v>
+        <v>22.43</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Gross 16.88 incl. 20% VAT; tier prices from 3 pcs</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1186,30 +1286,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter - GN 1/1 (530 x 325 mm) - 65 mm - Inhalt 9,0 l - Polycarbonat</t>
+          <t>Vogue Polycarbonat GN-Behälter GN1/1 65mm</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-behaelter-gn-1-1-530-x-325-mm-65-mm-inhalt-9-0-l-polycarbonat/530100-C</t>
+          <t>https://www.gastroladen.at/3020@GN-U224/Vogue-Polycarbonat-GN-Beh%C3%A4lter-GN1-1-65mm.htm</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>13.9</v>
+        <v>12.49</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -1217,7 +1317,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>13.9</v>
+        <v>10.41</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1226,7 +1326,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Regular price 22.55</t>
+          <t>Currently 'zurzeit nicht am Lager' (out of stock)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1237,31 +1337,35 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GN 1/2 polycarbonate container, 150 mm deep</t>
+          <t>GN 1/1 polycarbonate container, 65 mm deep</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PC GN 1/2 Höhe 150 mm schwarz</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>Gastronormbehälter GN 1/1 x 65 mm GN 94 Polycarbonat transparent</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/PC-GN-1-2-Hoehe-150-mm-schwarz.html</t>
+          <t>https://www.intergastro.at/gastronormbehaelter-gn-1-1-x-65-mm-gn-94-polycarbonat-transparent-252042</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7.29</v>
+        <v>14.07</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1273,7 +1377,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>7.29</v>
+        <v>14.07</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1282,7 +1386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>'jetzt' price; regular 10.35</t>
+          <t>Gross 16.88 incl. 20% VAT; tier prices from 3 pcs</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1293,35 +1397,35 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GN 1/2 polycarbonate container, 150 mm deep</t>
+          <t>GN 1/1 polycarbonate container, 65 mm deep</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Vogue GN-Behälter 1/2 Polycarbonat - Tiefe 150 mm</t>
+          <t>GN-Behälter - GN 1/1 (530 x 325 mm) - 65 mm - Inhalt 9,0 l - Polycarbonat</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/vogue-gn-behaelter-12-polycarbonat-tiefe-150-mm-u230</t>
+          <t>https://shopbuero.com/gn-behaelter-gn-1-1-530-x-325-mm-65-mm-inhalt-9-0-l-polycarbonat/530100-C</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9.99</v>
+        <v>13.9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1437,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>9.99</v>
+        <v>13.9</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1342,7 +1446,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Sale price (normal 11.89); min. qty 4. Schneider equivalent 17.39</t>
+          <t>Regular price 22.55</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1362,26 +1466,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Hendi Gastronorm-Behälter 1/2, GN 1/2, 9,5L, Transparent, 325x265x(H)150mm – Polycarbonat</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Hendi</t>
-        </is>
-      </c>
+          <t>PC GN 1/2 Höhe 150 mm schwarz</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-gn-1-2-9-5-l-polykarbonat-transparent-325-x-265-x-h-150-mm</t>
+          <t>https://www.allpax.at/product_info.php/info/PC-GN-1-2-Hoehe-150-mm-schwarz.html</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>18.75</v>
+        <v>7.29</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1393,14 +1493,18 @@
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>18.75</v>
+        <v>7.29</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>'jetzt' price; regular 10.35</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1418,45 +1522,53 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Vogue Polycarbonat GN-Behälter GN1/2 150mm</t>
+          <t>(6 Stück) CAMBRO CAMVIEW Copolymer-Behälter GN 1/2 - Höhe 150mm - BPA-frei</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Cambro</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/3020@GN-U230/Vogue-Polycarbonat-GN-Beh%C3%A4lter-GN1-2-150mm.htm</t>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-cambro-camview-r-copolymer-behaelter-gn-1-2-transparent-hoehe-150mm-bpa-frei-26cv135</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>10.09</v>
+        <v>60.99</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="n">
-        <v>8.41</v>
+        <v>10.17</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Copolyester (Tritan-type), not polycarbonate; no PC GN 1/2 150 mm found in GGM sitemap</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1474,26 +1586,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastro Star</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Gastronorm Behälter GN 1/2 GN 96 BLACK Polycarbonat schwarz H 150 mm</t>
+          <t>RIEBER GN 1/2 Polycarbonat-Behälter - Tiefe 150mm</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Rieber</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/gastronorm-behaelter-gn-1-2-gn-96-black-polycarbonat-schwarz-h-150-mm-1016774</t>
+          <t>https://www.gastro-star.at/produkt/riebergn12polycarbonat-behaelter-tiefe150mm/</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.17</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1505,7 +1617,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>10.17</v>
+        <v>21</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1514,7 +1626,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Black PC; gross 12.20</t>
+          <t>Gross 25.20</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1534,26 +1646,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Jungheinrich PROFISHOP Austria</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Stalgast ARAVEN Gastronormbehälter mit Deckel, Polypropylen, GN 1/2 (150 mm)</t>
+          <t>Vogue GN-Behälter 1/2 Polycarbonat - Tiefe 150 mm</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Stalgast / Araven</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-araven-gastronormbehaelter-mit-deckel-polypropylen-gn-1-2-150-mm-928334-347849/</t>
+          <t>https://www.gastro-hero.at/products/vogue-gn-behaelter-12-polycarbonat-tiefe-150-mm-u230</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>37.9</v>
+        <v>9.99</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1565,16 +1677,16 @@
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>37.9</v>
+        <v>9.99</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Polypropylene (not polycarbonate) and includes lid; no PC GN 1/2 150 mm found</t>
+          <t>Sale price (normal 11.89); min. qty 4. Schneider equivalent 17.39</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1594,26 +1706,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter - GN 1/2 (325 x 265 mm) - 150 mm - Inhalt 9,0 l - Polycarbonat</t>
+          <t>Hendi Gastronorm-Behälter 1/2, GN 1/2, 9,5L, Transparent, 325x265x(H)150mm – Polycarbonat</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-behaelter-gn-1-2-325-x-265-mm-150-mm-inhalt-9-0-l-polycarbonat/530112-C</t>
+          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-gn-1-2-9-5-l-polykarbonat-transparent-325-x-265-x-h-150-mm</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>10.9</v>
+        <v>18.75</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1625,18 +1737,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>10.9</v>
+        <v>18.75</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Regular price 17.20</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1645,39 +1753,39 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GN 1/3 polypropylene container, 100 mm deep</t>
+          <t>GN 1/2 polycarbonate container, 150 mm deep</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Araven GN1/3 Lebensmittelbehälter blau 100 mm</t>
+          <t>Vogue Polycarbonat GN-Behälter GN1/2 150mm</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Araven</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/araven-gn13-lebensmittelbehaelter-blau-100-mm-gp579</t>
+          <t>https://www.gastroladen.at/3020@GN-U230/Vogue-Polycarbonat-GN-Beh%C3%A4lter-GN1-2-150mm.htm</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>18.09</v>
+        <v>10.09</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1685,18 +1793,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>18.09</v>
+        <v>8.41</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Polypropylene, colour-coded blue; sale price (normal 18.59)</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1705,35 +1809,35 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>GN 1/3 polypropylene container, 100 mm deep</t>
+          <t>GN 1/2 polycarbonate container, 150 mm deep</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Hendi Gastronorm-Behälter 1/3, GN 1/3, 4L, Transparent, 325x176x(H)100mm – Polypropylen</t>
+          <t>Gastronorm Behälter GN 1/2 GN 96 BLACK Polycarbonat schwarz H 150 mm</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-haccp-aufbewahrungsbehaelter-gn-1-3-4-l-transparent-325-x-176-x-h-100-mm</t>
+          <t>https://www.intergastro.at/gastronorm-behaelter-gn-1-2-gn-96-black-polycarbonat-schwarz-h-150-mm-1016774</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.6</v>
+        <v>10.17</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1745,14 +1849,18 @@
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>18.6</v>
+        <v>10.17</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Black PC; gross 12.20</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1761,39 +1869,39 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>GN 1/3 polypropylene container, 100 mm deep</t>
+          <t>GN 1/2 polycarbonate container, 150 mm deep</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cambro Polypropylen GN 1/3 Behälter 100mm</t>
+          <t>Stalgast ARAVEN Gastronormbehälter mit Deckel, Polypropylen, GN 1/2 (150 mm)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>Stalgast / Araven</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/3030@GN-DW504/Cambro-Polypropylen-GN-1-3-Beh%C3%A4lter-100mm.htm</t>
+          <t>https://www.jh-profishop.at/p/stalgast-araven-gastronormbehaelter-mit-deckel-polypropylen-gn-1-2-150-mm-928334-347849/</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>6.98</v>
+        <v>37.9</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1801,16 +1909,16 @@
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>5.82</v>
+        <v>37.9</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3.6 l</t>
+          <t>Polypropylene (not polycarbonate) and includes lid; no PC GN 1/2 150 mm found</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1821,35 +1929,35 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GN 1/3 polypropylene container, 100 mm deep</t>
+          <t>GN 1/2 polycarbonate container, 150 mm deep</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter GN 1/3 x 100 mm Kunststoff transparent-weiß (Polypropylen)</t>
+          <t>GN-Behälter - GN 1/2 (325 x 265 mm) - 150 mm - Inhalt 9,0 l - Polycarbonat</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/gn-behaelter-gn-1-3-x-100-mm-kunststoff-transparent-weiss-251459</t>
+          <t>https://shopbuero.com/gn-behaelter-gn-1-2-325-x-265-mm-150-mm-inhalt-9-0-l-polycarbonat/530112-C</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1861,7 +1969,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1870,7 +1978,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Gross 12.00</t>
+          <t>Regular price 17.20</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1890,26 +1998,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Jungheinrich PROFISHOP Austria</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Stalgast Gastronormbehälter, Polypropylen, GN 1/3 (100 mm)</t>
+          <t>(12 Stück) Polypropylen-Behälter GN 1/3 - Milchig - Höhe: 100mm</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-gastronormbehaelter-polypropylen-gn-1-3-100-mm-928342-347857/</t>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polypropylen-behaelter-gn-1-3-milchig-hoehe-100mm-gpp13100</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>14</v>
+        <v>39.99</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1917,18 +2025,26 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="n">
-        <v>14</v>
+        <v>3.33</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>The 6-piece version of the same item is listed at 175.99 net (looks like a listing error; not used)</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1946,26 +2062,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Gastro Star</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>GN-Behälter - Inhalt 3,8 l - GN 1/3 (325 x 176 mm) - 100 mm - Polypropylen</t>
+          <t>Polypropylen Behälter GN 1/3 – 325x176x100mm</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-behaelter-inhalt-3-8-l-gn-1-3-325-x-176-mm-100-mm-polypropylen/530021-C</t>
+          <t>https://www.gastro-star.at/produkt/polypropylenbehaeltergn13-325x176x100mm/</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1977,7 +2093,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -1986,7 +2102,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Regular price 6.90</t>
+          <t>4 l; gross 5.70</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1997,11 +2113,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GN 1/1 polypropylene lid</t>
+          <t>GN 1/3 polypropylene container, 100 mm deep</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2011,21 +2127,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Schneider PP GN 1/1 Deckel, einrastend</t>
+          <t>Araven GN1/3 Lebensmittelbehälter blau 100 mm</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Araven</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneider-pp-gn-11-deckel-einrastend-530005</t>
+          <t>https://www.gastro-hero.at/products/araven-gn13-lebensmittelbehaelter-blau-100-mm-gp579</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>11.69</v>
+        <v>18.09</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2037,7 +2153,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>11.69</v>
+        <v>18.09</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -2046,7 +2162,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Min. qty 4</t>
+          <t>Polypropylene, colour-coded blue; sale price (normal 18.59)</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2057,11 +2173,11 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GN 1/1 polypropylene lid</t>
+          <t>GN 1/3 polypropylene container, 100 mm deep</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2071,7 +2187,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hendi Gastronorm-Deckel, GN 1/1, Transparent, 530x325mm</t>
+          <t>Hendi Gastronorm-Behälter 1/3, GN 1/3, 4L, Transparent, 325x176x(H)100mm – Polypropylen</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2081,11 +2197,11 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-gastronorm-deckel-gn-1-1-transparent-530-x-325-mm</t>
+          <t>https://www.gastrodax.de/hendi-haccp-aufbewahrungsbehaelter-gn-1-3-4-l-transparent-325-x-176-x-h-100-mm</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>16.66</v>
+        <v>18.6</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2097,18 +2213,14 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>16.66</v>
+        <v>18.6</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Lid for Hendi polypropylene GN containers; lid material not explicitly stated</t>
-        </is>
-      </c>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2117,11 +2229,11 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GN 1/1 polypropylene lid</t>
+          <t>GN 1/3 polypropylene container, 100 mm deep</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2131,7 +2243,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Cambro biegsamer Polypropylen Deckel GN 1/1</t>
+          <t>Cambro Polypropylen GN 1/3 Behälter 100mm</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2141,11 +2253,11 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/3030@GN-DM743/Cambro-biegsamer-Polypropylen-Deckel-GN-1-1.htm</t>
+          <t>https://www.gastroladen.at/3030@GN-DW504/Cambro-Polypropylen-GN-1-3-Beh%C3%A4lter-100mm.htm</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.09</v>
+        <v>6.98</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2157,7 +2269,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>9.24</v>
+        <v>5.82</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -2166,7 +2278,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Flexible PP lid with seal</t>
+          <t>3.6 l</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2177,11 +2289,11 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GN 1/1 polypropylene lid</t>
+          <t>GN 1/3 polypropylene container, 100 mm deep</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2191,21 +2303,21 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>GN Deckel GN 89 GN 1/1 Polypropylen weiß</t>
+          <t>GN-Behälter GN 1/3 x 100 mm Kunststoff transparent-weiß (Polypropylen)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/gn-deckel-gn-89-gn-1-1-polypropylen-weiss-252554</t>
+          <t>https://www.intergastro.at/gn-behaelter-gn-1-3-x-100-mm-kunststoff-transparent-weiss-251459</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2329,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="3" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2338,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Gross 9.00</t>
+          <t>Gross 12.00</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2237,35 +2349,35 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GN 1/1 polypropylene lid</t>
+          <t>GN 1/3 polypropylene container, 100 mm deep</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>GN-Deckel - einrastend - GN 1/1 (530 x 325 mm) - Polypropylen</t>
+          <t>Stalgast Gastronormbehälter, Polypropylen, GN 1/3 (100 mm)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/gn-deckel-einrastend-gn-1-1-530-x-325-mm-polypropylen/530005-C</t>
+          <t>https://www.jh-profishop.at/p/stalgast-gastronormbehaelter-polypropylen-gn-1-3-100-mm-928342-347857/</t>
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2277,18 +2389,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t>EXACT</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Regular price 7.65. APS PP lid 82101-B: 4.20</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2297,31 +2405,35 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, PP, single tip</t>
+          <t>GN 1/3 polypropylene container, 100 mm deep</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Quetschflasche PE 0,45 l, mit Schraubdeckel, 6 Stück</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>GN-Behälter - Inhalt 3,8 l - GN 1/3 (325 x 176 mm) - 100 mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/Quetschflasche-PE-0-45-l-mit-Schraubdeckel-6-St-uuml-ck.html</t>
+          <t>https://shopbuero.com/gn-behaelter-inhalt-3-8-l-gn-1-3-325-x-176-mm-100-mm-polypropylen/530021-C</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2329,24 +2441,20 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>set of 6</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>1.42</v>
+        <v>4.5</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>450 ml, polyethylene (not PP); site shows 1 pc = 1.42</t>
+          <t>Regular price 6.90</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2357,35 +2465,35 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Schneider PP Quetschflasche transparent 500 ml</t>
+          <t>(12 Stück) Polypropylen-Deckel GN 1/1 - Milchig - mit 24 Codierclips</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneider-pp-quetschflasche-transparent-500-ml-200491</t>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polypropylen-deckel-gn-1-1-milchig-mit-24-codierclips-gppl11-12</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>3.89</v>
+        <v>29.49</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2393,11 +2501,15 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>set of 12 (per title)</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="n">
-        <v>3.89</v>
+        <v>2.46</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -2406,7 +2518,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Min. qty 12</t>
+          <t>Title says 12 pcs but spec table says 'Set Menge 6 Stk' - conflicting; if 6 pcs, net/pc would be 4.92</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2417,35 +2529,35 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>Gastro Star</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Contacto Quetschflasche 0,5 l</t>
+          <t>Polypropylen Deckel GN 1/1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-quetschflasche-0-5-l</t>
+          <t>https://www.gastro-star.at/produkt/polypropylendeckelgn11/</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.32</v>
+        <v>5.55</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2457,16 +2569,16 @@
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="3" t="n">
-        <v>2.32</v>
+        <v>5.55</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Polyethylene (not PP), bottom-fill FIFO type with silicone valve; sale price, normal 2.90</t>
+          <t>Gross 6.66</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2477,39 +2589,39 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Vogue Quetschflasche extra breit klar 454ml</t>
+          <t>Schneider PP GN 1/1 Deckel, einrastend</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/G16771B@GN-E092/Vogue-Quetschflasche-extra-breit-klar-454ml.htm</t>
+          <t>https://www.gastro-hero.at/products/schneider-pp-gn-11-deckel-einrastend-530005</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4.59</v>
+        <v>11.69</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2517,16 +2629,16 @@
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="3" t="n">
-        <v>3.83</v>
+        <v>11.69</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>454 ml, polyethylene (not PP), wide neck, single nozzle; sold singly</t>
+          <t>Min. qty 4</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2537,35 +2649,35 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Quetschflasche 490 ml transparent Ø 70 mm H 200 mm (6er Set)</t>
+          <t>Hendi Gastronorm-Deckel, GN 1/1, Transparent, 530x325mm</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/quetschflasche-490-ml-transparent-70-mm-h-200-mm-985062</t>
+          <t>https://www.gastrodax.de/hendi-gastronorm-deckel-gn-1-1-transparent-530-x-325-mm</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.73</v>
+        <v>16.66</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2573,15 +2685,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>set of 6</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="3" t="n">
-        <v>1.46</v>
+        <v>16.66</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -2590,7 +2698,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>490 ml; material polyethylene (not PP); price per set of 6, gross 10.48</t>
+          <t>Lid for Hendi polypropylene GN containers; lid material not explicitly stated</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2601,39 +2709,39 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 1000 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>APS Quetschflasche, transparent, 1,025 L</t>
+          <t>Cambro biegsamer Polypropylen Deckel GN 1/1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Cambro</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/aps-quetschflasche-transparent-1025-l-aps93259</t>
+          <t>https://www.gastroladen.at/3030@GN-DM743/Cambro-biegsamer-Polypropylen-Deckel-GN-1-1.htm</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>2.09</v>
+        <v>11.09</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -2641,16 +2749,16 @@
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="3" t="n">
-        <v>2.09</v>
+        <v>9.24</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1025 ml, polyethylene (not PP); min. qty 2</t>
+          <t>Flexible PP lid with seal</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2661,35 +2769,35 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 1000 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Contacto Quetschflasche 0,95 l</t>
+          <t>GN Deckel GN 89 GN 1/1 Polypropylen weiß</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-quetschflasche-0-95-l</t>
+          <t>https://www.intergastro.at/gn-deckel-gn-89-gn-1-1-polypropylen-weiss-252554</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2.76</v>
+        <v>7.5</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2701,16 +2809,16 @@
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="3" t="n">
-        <v>2.76</v>
+        <v>7.5</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>950 ml, polyethylene, FIFO bottom-fill; sale price, normal 3.45</t>
+          <t>Gross 9.00</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2721,39 +2829,39 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 1000 ml, PP, single tip</t>
+          <t>GN 1/1 polypropylene lid</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Vogue Quetschflasche klar 990ml</t>
+          <t>GN-Deckel - einrastend - GN 1/1 (530 x 325 mm) - Polypropylen</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/G16771B@GN-W832/Vogue-Quetschflasche-klar-990ml.htm</t>
+          <t>https://shopbuero.com/gn-deckel-einrastend-gn-1-1-530-x-325-mm-polypropylen/530005-C</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3.79</v>
+        <v>5</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2761,16 +2869,16 @@
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="3" t="n">
-        <v>3.16</v>
+        <v>5</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>990 ml, polyethylene (not PP)</t>
+          <t>Regular price 7.65. APS PP lid 82101-B: 4.20</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2781,47 +2889,47 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Quetschflasche PE 0,45 l, mit Schraubdeckel, 6 Stück</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Quetschflasche-PE-0-45-l-mit-Schraubdeckel-6-St-uuml-ck.html</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Squeeze bottle 1000 ml, PP, single tip</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Intergastro (AT shop)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Quetschflasche 1025 ml transparent Ø 80 mm H 265 mm</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>APS</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.intergastro.at/quetschflasche-1025-ml-transparent-80-mm-h-265-mm-985068</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>excl.</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="n">
-        <v>1.95</v>
+        <v>1.42</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -2830,7 +2938,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1025 ml; material polyethylene (not PP); gross 2.34</t>
+          <t>450 ml, polyethylene (not PP); site shows 1 pc = 1.42</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2841,35 +2949,35 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, triple tip</t>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Schneider Quetschflasche 950 ml, 3 Öffnungen</t>
+          <t>(12 Stück) Quetschflasche mit mittlerer Membran - 473ml</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneider-quetschflasche-950-ml-3-oeffnungen-150621</t>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-quetschflasche-mit-mittlerer-membran-473ml-ffo-002</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>6.89</v>
+        <v>51.99</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2877,20 +2985,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>6.89</v>
+        <v>4.33</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Triple tip PP but 950 ml instead of 500 ml; sale price (normal 7.09); min. qty 8</t>
+          <t>473 ml, FIFO type with valve; material not stated</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2901,39 +3013,39 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, triple tip</t>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Vogue transparente Quetschflasche mit 3 Spritzdüsen 68cl</t>
+          <t>Schneider PP Quetschflasche transparent 500 ml</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Vogue</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/G16771B@GN-CW725/Vogue-transparente-Quetschflasche-mit-3-Spritzd%C3%BCsen-68cl.htm</t>
+          <t>https://www.gastro-hero.at/products/schneider-pp-quetschflasche-transparent-500-ml-200491</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>3.98</v>
+        <v>3.89</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
@@ -2941,16 +3053,16 @@
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="3" t="n">
-        <v>3.32</v>
+        <v>3.89</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Triple tip but 680 ml instead of 500 ml; smallest triple-tip offered</t>
+          <t>Min. qty 12</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2961,35 +3073,35 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Squeeze bottle 500 ml, triple tip</t>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Quetschflasche Kunststoff 950 ml 3 Öffnungen transparent</t>
+          <t>Contacto Quetschflasche 0,5 l</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/quetschflasche-kunststoff-950-ml-3-oeffnungen-transparent-80-mm-h-291-mm-960754</t>
+          <t>https://www.gastrodax.de/contacto-quetschflasche-0-5-l</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4.44</v>
+        <v>2.32</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -3001,16 +3113,16 @@
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="3" t="n">
-        <v>4.44</v>
+        <v>2.32</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Triple tip PP bottle but 950 ml instead of 500 ml; no 500 ml triple-tip found</t>
+          <t>Polyethylene (not PP), bottom-fill FIFO type with silicone valve; sale price, normal 2.90</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3021,35 +3133,39 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Saucenspender (für Senf, Ketchup, Mayonnaise), 2 l</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Vogue Quetschflasche extra breit klar 454ml</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/p12858_Saucenspender.html</t>
+          <t>https://www.gastroladen.at/G16771B@GN-E092/Vogue-Quetschflasche-extra-breit-klar-454ml.htm</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>36.1</v>
+        <v>4.59</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -3057,7 +3173,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>36.1</v>
+        <v>3.83</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
@@ -3066,7 +3182,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Sauce pump dispenser 2 l (17x14x15.5 cm); price shown for default 2 l size; stand not mentioned</t>
+          <t>454 ml, polyethylene (not PP), wide neck, single nozzle; sold singly</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3077,35 +3193,35 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 500 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Hendi Pump-Saucenspender, 2,5L, Weiß</t>
+          <t>Quetschflasche 490 ml transparent Ø 70 mm H 200 mm (6er Set)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/hendi-pump-saucenspender-2-5l-wei-c3-9f-230x210x-h-250mm</t>
+          <t>https://www.intergastro.at/quetschflasche-490-ml-transparent-70-mm-h-200-mm-985062</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>26.89</v>
+        <v>8.73</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -3113,20 +3229,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="n">
-        <v>26.89</v>
+        <v>1.46</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>ABS housing/stand with pump</t>
+          <t>490 ml; material polyethylene (not PP); price per set of 6, gross 10.48</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3137,35 +3257,35 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Hendi Pump-Saucenspender, 2,5L, Weiß, 230x210x(H)327mm</t>
+          <t>(6 Stück) Quetschflasche mit mittlerer Membran - 946ml</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-pump-sossenspender-weiss</t>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-quetschflasche-mit-mittlerer-membran-946ml-ffo-005</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>19.76</v>
+        <v>35.99</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -3173,20 +3293,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="n">
-        <v>19.76</v>
+        <v>6</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>ABS housing/stand with PP sauce container, lid and pump</t>
+          <t>946 ml, FIFO type; material not stated</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3197,39 +3321,39 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Araven Soßenspender GN 1/9 Transparent 1,5L</t>
+          <t>APS Quetschflasche, transparent, 1,025 L</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Araven</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/3300@GN-CR821/Araven-So%C3%9Fenspender-GN-1-9-Transparent-1-5L.htm</t>
+          <t>https://www.gastro-hero.at/products/aps-quetschflasche-transparent-1025-l-aps93259</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>36.9</v>
+        <v>2.09</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -3237,7 +3361,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>30.75</v>
+        <v>2.09</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3246,7 +3370,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>PP pump dispenser 1.5 l; stand only included in 2-/3-piece sets (3-set with acrylic stand 157.90)</t>
+          <t>1025 ml, polyethylene (not PP); min. qty 2</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3257,35 +3381,35 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Druckknopf-Dosierspender rot 2 ltr Ø 98 mm H 440 mm</t>
+          <t>Contacto Quetschflasche 0,95 l</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/druckknopf-dosierspender-rot-2-ltr-98-mm-h-440-mm-100247</t>
+          <t>https://www.gastrodax.de/contacto-quetschflasche-0-95-l</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>93.66</v>
+        <v>2.76</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -3297,7 +3421,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>93.66</v>
+        <v>2.76</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
@@ -3306,7 +3430,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Free-standing glass/stainless push-button sauce pump dispenser, 2 l; gross 112.39</t>
+          <t>950 ml, polyethylene, FIFO bottom-fill; sale price, normal 3.45</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3317,39 +3441,39 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Ketchup/sauce pump dispenser with stand</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Dosierspender - mit Druckknopf - 18,0 x 14,5 x 29,0 cm - Inhalt 2,0 l - Polyethylen</t>
+          <t>Vogue Quetschflasche klar 990ml</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/dosierspender-mit-druckknopf-18-0-x-14-5-x-29-0-cm-inhalt-2-0-l-polyethylen/154710-C</t>
+          <t>https://www.gastroladen.at/G16771B@GN-W832/Vogue-Quetschflasche-klar-990ml.htm</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>30.5</v>
+        <v>3.79</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3357,7 +3481,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>30.5</v>
+        <v>3.16</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
@@ -3366,7 +3490,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Push-button sauce pump dispenser 2 l, free-standing; regular price 49.20</t>
+          <t>990 ml, polyethylene (not PP)</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3377,35 +3501,35 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Squeeze bottle 1000 ml, PP, single tip</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett PRO 53x32 W-R</t>
+          <t>Quetschflasche 1025 ml transparent Ø 80 mm H 265 mm</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Bartscher</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/Schneidbrett-PRO-53x32-W-R.html</t>
+          <t>https://www.intergastro.at/quetschflasche-1025-ml-transparent-80-mm-h-265-mm-985068</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>26.95</v>
+        <v>1.95</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3417,16 +3541,16 @@
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="3" t="n">
-        <v>26.95</v>
+        <v>1.95</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>HDPE white, 20 mm plate, juice groove, 530x325x24 mm incl. feet</t>
+          <t>1025 ml; material polyethylene (not PP); gross 2.34</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3437,11 +3561,11 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Squeeze bottle 500 ml, triple tip</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3451,21 +3575,21 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett GN 1/1 - 53 x 32,5 x 1,5 cm - HDPE blau</t>
+          <t>Schneider Quetschflasche 950 ml, 3 Öffnungen</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneidbrett-gn-1-1-53-x-32-5-x-1-5-cm-hdpe-blau</t>
+          <t>https://www.gastro-hero.at/products/schneider-quetschflasche-950-ml-3-oeffnungen-150621</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>33.69</v>
+        <v>6.89</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3477,16 +3601,16 @@
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="3" t="n">
-        <v>33.69</v>
+        <v>6.89</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15 mm instead of 20 mm; sale price (normal 39.29)</t>
+          <t>Triple tip PP but 950 ml instead of 500 ml; sale price (normal 7.09); min. qty 8</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3497,39 +3621,39 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Squeeze bottle 500 ml, triple tip</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Hendi Schneidbrett HACCP Gastronorm 1/1, Weiß, 530x325mm</t>
+          <t>Vogue transparente Quetschflasche mit 3 Spritzdüsen 68cl</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Vogue</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-gastronorm-1-1-gn-1-1-weiss-530-x-325-mm</t>
+          <t>https://www.gastroladen.at/G16771B@GN-CW725/Vogue-transparente-Quetschflasche-mit-3-Spritzd%C3%BCsen-68cl.htm</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>20.95</v>
+        <v>3.98</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3537,16 +3661,16 @@
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="3" t="n">
-        <v>20.95</v>
+        <v>3.32</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>15 mm thick instead of 20 mm; all HACCP colours same price</t>
+          <t>Triple tip but 680 ml instead of 500 ml; smallest triple-tip offered</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3557,39 +3681,39 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Squeeze bottle 500 ml, triple tip</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Bartscher Schneidbrett PRO 53x32 W-R</t>
+          <t>Quetschflasche Kunststoff 950 ml 3 Öffnungen transparent</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Bartscher</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/2310@A120511/Bartscher-Schneidbrett-PRO-53x32-W-R.htm</t>
+          <t>https://www.intergastro.at/quetschflasche-kunststoff-950-ml-3-oeffnungen-transparent-80-mm-h-291-mm-960754</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>29.49</v>
+        <v>4.44</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3597,16 +3721,16 @@
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="3" t="n">
-        <v>24.57</v>
+        <v>4.44</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>PE, 20 mm plate, HACCP white, rubber feet (530x24x325 overall)</t>
+          <t>Triple tip PP bottle but 950 ml instead of 500 ml; no 500 ml triple-tip found</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3617,35 +3741,31 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>HACCP Schneidbrett Polyethylen weiß 530 x 325 mm H 20 mm</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>WAS Germany</t>
-        </is>
-      </c>
+          <t>Saucenspender (für Senf, Ketchup, Mayonnaise), 2 l</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/haccp-schneidbrett-polyethylen-weiss-530-mm-x-325-mm-h-20-mm-159115</t>
+          <t>https://www.allpax.at/product_info.php/info/p12858_Saucenspender.html</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>22.09</v>
+        <v>36.1</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -3657,16 +3777,16 @@
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="3" t="n">
-        <v>22.09</v>
+        <v>36.1</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>White; other HACCP colours listed separately; gross 26.51</t>
+          <t>Sauce pump dispenser 2 l (17x14x15.5 cm); price shown for default 2 l size; stand not mentioned</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3677,35 +3797,35 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Jungheinrich PROFISHOP Austria</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Stalgast Schneidbrett, HACCP, Farbe weiß, GN1/1, Stärke 15 mm</t>
+          <t>Ketchup / Saucenspender - 2 Liter - Polypropylen - mit Pumpe</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-haccp-farbe-weiss-gn1-1-staerke-15-mm-927572-346785/</t>
+          <t>https://www.ggmgastro.com/de-at-eur/ketchup-saucenspender-2-liter-polypropylen-mit-pumpe-ksp2</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>23.9</v>
+        <v>28.99</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -3717,16 +3837,16 @@
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="3" t="n">
-        <v>23.9</v>
+        <v>28.99</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>15 mm instead of 20 mm; material polypropylene (not PE); all 6 HACCP colours same price</t>
+          <t>210x220x210 mm, PP with pump</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3737,35 +3857,35 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>HACCP Schneidbrett - GN 1/1 - weiß - 2,0 cm - Polyethylen</t>
+          <t>Hendi Pump-Saucenspender, 2,5L, Weiß</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/haccp-schneidbrett-gn-1-1-weiss-2-0-cm-polyethylen/1830530-A</t>
+          <t>https://www.gastro-hero.at/products/hendi-pump-saucenspender-2-5l-wei-c3-9f-230x210x-h-250mm</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>18</v>
+        <v>26.89</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -3777,7 +3897,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="3" t="n">
-        <v>18</v>
+        <v>26.89</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -3786,7 +3906,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Regular price 27.00</t>
+          <t>ABS housing/stand with pump</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3797,31 +3917,35 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett farbig 600 x 400 x 20 mm</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>Hendi Pump-Saucenspender, 2,5L, Weiß, 230x210x(H)327mm</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/p30393_Schneidbrett-farbig-600-x-400-x-20-mm.html</t>
+          <t>https://www.gastrodax.de/hendi-pump-sossenspender-weiss</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>49.39</v>
+        <v>19.76</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3833,16 +3957,16 @@
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="3" t="n">
-        <v>49.39</v>
+        <v>19.76</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>600x400x20 mm, 5 colours, rubber feet; material not stated. Bartscher 60x40 white (16 mm) 34.61</t>
+          <t>ABS housing/stand with PP sauce container, lid and pump</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3853,39 +3977,39 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Schneidebrett Gastro-M 600x400 weiß</t>
+          <t>Araven Soßenspender GN 1/9 Transparent 1,5L</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Gastro-M</t>
+          <t>Araven</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneidebrett-gastro-m-600x400-weiss-gn344</t>
+          <t>https://www.gastroladen.at/3300@GN-CR821/Araven-So%C3%9Fenspender-GN-1-9-Transparent-1-5L.htm</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>48.9</v>
+        <v>36.9</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
@@ -3893,7 +4017,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="3" t="n">
-        <v>48.9</v>
+        <v>30.75</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -3902,7 +4026,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>600x400x20 mm; material not stated on page; sale price (normal 52.90)</t>
+          <t>PP pump dispenser 1.5 l; stand only included in 2-/3-piece sets (3-set with acrylic stand 157.90)</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3913,35 +4037,35 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Hendi Schneidbretter HACCP 600x400, Weiß</t>
+          <t>Druckknopf-Dosierspender rot 2 ltr Ø 98 mm H 440 mm</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-600-x-400-mm-weiss</t>
+          <t>https://www.intergastro.at/druckknopf-dosierspender-rot-2-ltr-98-mm-h-440-mm-100247</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>33.5</v>
+        <v>93.66</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3953,7 +4077,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="3" t="n">
-        <v>33.5</v>
+        <v>93.66</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -3962,7 +4086,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>18 mm thick instead of 20 mm</t>
+          <t>Free-standing glass/stainless push-button sauce pump dispenser, 2 l; gross 112.39</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -3973,39 +4097,39 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>Ketchup/sauce pump dispenser with stand</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Bartscher Schneidbrett 60x40 W</t>
+          <t>Dosierspender - mit Druckknopf - 18,0 x 14,5 x 29,0 cm - Inhalt 2,0 l - Polyethylen</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Bartscher</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/2310@A120592/Bartscher-Schneidbrett-60x40-W.htm</t>
+          <t>https://shopbuero.com/dosierspender-mit-druckknopf-18-0-x-14-5-x-29-0-cm-inhalt-2-0-l-polyethylen/154710-C</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>34.9</v>
+        <v>30.5</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
@@ -4013,7 +4137,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="3" t="n">
-        <v>29.08</v>
+        <v>30.5</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
@@ -4022,7 +4146,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>PE, 16 mm plate (20 mm incl. feet), HACCP white</t>
+          <t>Push-button sauce pump dispenser 2 l, free-standing; regular price 49.20</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4033,35 +4157,35 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett Polyethylen weiß mit Saftrille 600 x 400 mm</t>
+          <t>Schneidbrett PRO 53x32 W-R</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Bartscher</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/schneidbrett-polyethylen-weiss-mit-saftrille-600-mm-x-400-mm-159019</t>
+          <t>https://www.allpax.at/product_info.php/info/Schneidbrett-PRO-53x32-W-R.html</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>35.05</v>
+        <v>26.95</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -4073,7 +4197,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="3" t="n">
-        <v>35.05</v>
+        <v>26.95</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -4082,7 +4206,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>20 mm thick, with juice groove; gross 42.06</t>
+          <t>HDPE white, 20 mm plate, juice groove, 530x325x24 mm incl. feet</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4093,35 +4217,35 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 600x400x20 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Jungheinrich PROFISHOP Austria</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Stalgast Schneidbrett, HACCP, Farbe weiß, 600 x 400 x 18 mm</t>
+          <t>Schneidebrett - 325x530mm - HACCP-Konform - Weiß</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-haccp-farbe-weiss-600-x-400-x-18-mm-bxtxh-928737-348334/</t>
+          <t>https://www.ggmgastro.com/de-at-eur/schneidebrett-325x530mm-haccp-konform-weiss-sbp53w</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>27.9</v>
+        <v>26.49</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -4133,16 +4257,16 @@
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="3" t="n">
-        <v>27.9</v>
+        <v>26.49</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>18 mm instead of 20 mm; material PP (not PE); blue/yellow/green/brown 28.90</t>
+          <t>PE, 325x530x20 mm</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4153,11 +4277,11 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4167,7 +4291,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett GN 1/2 - 32,5 x 26,5 x 1,2 cm - HDPE weiß</t>
+          <t>Schneidbrett GN 1/1 - 53 x 32,5 x 1,5 cm - HDPE blau</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4177,11 +4301,11 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/schneidbrett-gn-1-2-32-5-x-26-5-x-1-2-cm-hdpe-weiss</t>
+          <t>https://www.gastro-hero.at/products/schneidbrett-gn-1-1-53-x-32-5-x-1-5-cm-hdpe-blau</t>
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>24.99</v>
+        <v>33.69</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -4193,16 +4317,16 @@
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="3" t="n">
-        <v>24.99</v>
+        <v>33.69</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>325x265x12 mm (GN 1/2) vs 300x200x10; no 300x200 board found</t>
+          <t>15 mm instead of 20 mm; sale price (normal 39.29)</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4213,11 +4337,11 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4227,7 +4351,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Hendi Schneidbrett mit Griff, Weiß, 300x200mm</t>
+          <t>Hendi Schneidbrett HACCP Gastronorm 1/1, Weiß, 530x325mm</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4237,11 +4361,11 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-schneidbrett-mit-griff-weiss-300-x-200-mm</t>
+          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-gastronorm-1-1-gn-1-1-weiss-530-x-325-mm</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>15.76</v>
+        <v>20.95</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -4253,16 +4377,16 @@
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="3" t="n">
-        <v>15.76</v>
+        <v>20.95</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>300x200x10 mm HDPE, with handle</t>
+          <t>15 mm thick instead of 20 mm; all HACCP colours same price</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4273,11 +4397,11 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4287,21 +4411,21 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Hygiplas HDPE kleines Schneidebrett weiß 300x225x12mm</t>
+          <t>Bartscher Schneidbrett PRO 53x32 W-R</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Hygiplas</t>
+          <t>Bartscher</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/2310@GN-HC867/Hygiplas-HDPE-kleines-Schneidebrett-wei%C3%9F-300x-225x12mm.htm</t>
+          <t>https://www.gastroladen.at/2310@A120511/Bartscher-Schneidbrett-PRO-53x32-W-R.htm</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>29.49</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4313,16 +4437,16 @@
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="3" t="n">
-        <v>7.41</v>
+        <v>24.57</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>300x225x12 mm vs 300x200x10</t>
+          <t>PE, 20 mm plate, HACCP white, rubber feet (530x24x325 overall)</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4333,11 +4457,11 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4347,7 +4471,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Schneidbrett Polyethylen weiß 300 x 200 mm H 15 mm</t>
+          <t>HACCP Schneidbrett Polyethylen weiß 530 x 325 mm H 20 mm</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4357,11 +4481,11 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/schneidbrett-polyethylen-weiss-300-mm-x-200-mm-h-15-mm-158986</t>
+          <t>https://www.intergastro.at/haccp-schneidbrett-polyethylen-weiss-530-mm-x-325-mm-h-20-mm-159115</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>8.74</v>
+        <v>22.09</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4373,16 +4497,16 @@
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="3" t="n">
-        <v>8.74</v>
+        <v>22.09</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>15 mm thick instead of 10 mm; gross 10.49</t>
+          <t>White; other HACCP colours listed separately; gross 26.51</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4393,11 +4517,11 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>HACCP cutting board PE 300x200x10 mm</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4407,7 +4531,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Stalgast Schneidbrett, rutschfest 270x190x9 mm, schwarz</t>
+          <t>Stalgast Schneidbrett, HACCP, Farbe weiß, GN1/1, Stärke 15 mm</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4417,11 +4541,11 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-rutschfest-270x190x9-mm-schwarz-928715-348311/</t>
+          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-haccp-farbe-weiss-gn1-1-staerke-15-mm-927572-346785/</t>
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>16.3</v>
+        <v>23.9</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -4433,16 +4557,16 @@
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="3" t="n">
-        <v>16.3</v>
+        <v>23.9</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>270x190x9 mm, black non-slip board, not HACCP colour-coded</t>
+          <t>15 mm instead of 20 mm; material polypropylene (not PE); all 6 HACCP colours same price</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4453,35 +4577,35 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 530x325x20 mm (GN 1/1)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>AmerBox Pizzaballenbox 60 x 40 x 9,5 cm</t>
+          <t>HACCP Schneidbrett - GN 1/1 - weiß - 2,0 cm - Polyethylen</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>AmerBox</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-9-5-cm.html</t>
+          <t>https://shopbuero.com/haccp-schneidbrett-gn-1-1-weiss-2-0-cm-polyethylen/1830530-A</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>13.95</v>
+        <v>18</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -4493,16 +4617,16 @@
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="3" t="n">
-        <v>13.95</v>
+        <v>18</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>95 mm high and polyethylene (vs 100 mm PP), 18 l</t>
+          <t>Regular price 27.00</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4513,35 +4637,31 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Pizzateigbox 18 l 600x400x95 mm</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Hendi</t>
-        </is>
-      </c>
+          <t>Schneidbrett farbig 600 x 400 x 20 mm</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/pizzateigbox-18-l-600x400x95-mm</t>
+          <t>https://www.allpax.at/product_info.php/info/p30393_Schneidbrett-farbig-600-x-400-x-20-mm.html</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>28.49</v>
+        <v>49.39</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -4553,7 +4673,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="3" t="n">
-        <v>28.49</v>
+        <v>49.39</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
@@ -4562,7 +4682,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>95 mm high; material PET (not PP)</t>
+          <t>600x400x20 mm, 5 colours, rubber feet; material not stated. Bartscher 60x40 white (16 mm) 34.61</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -4573,35 +4693,35 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Hendi Pizzateigbox 600x400, AmerBox, Kitchen Line, 18L, 600x400x(H)95mm</t>
+          <t>Schneidebrett - EN 600x400 - HACCP-Konform - Weiß</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-pizzateig-box-kitchen-line-18-l-600-x-400-x-h-95-mm</t>
+          <t>https://www.ggmgastro.com/de-at-eur/schneidebrett-en-600x400-haccp-konform-weiss-sbp46w</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>21.38</v>
+        <v>29.49</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4613,16 +4733,16 @@
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="3" t="n">
-        <v>21.38</v>
+        <v>29.49</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>95 mm instead of 100 mm; material not stated</t>
+          <t>PE, 600x400x20 mm</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -4633,39 +4753,39 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble Stapelbarer Pizzateigbehälter 9,5cm (60x40)</t>
+          <t>Schneidebrett Gastro-M 600x400 weiß</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble</t>
+          <t>Gastro-M</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/x1090@GN-GN537/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-9-5cm.htm</t>
+          <t>https://www.gastro-hero.at/products/schneidebrett-gastro-m-600x400-weiss-gn344</t>
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>31.9</v>
+        <v>48.9</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
@@ -4673,7 +4793,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="3" t="n">
-        <v>26.58</v>
+        <v>48.9</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
@@ -4682,7 +4802,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>95 mm high and polyethylene (vs 100 mm PP)</t>
+          <t>600x400x20 mm; material not stated on page; sale price (normal 52.90)</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -4693,35 +4813,35 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Pizzaballenbehälter, Polyethylen 600x400x100 mm</t>
+          <t>Hendi Schneidbretter HACCP 600x400, Weiß</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/pizzaballenbehaelter-polyethylen-600x400x100-mm-bxtxh-1027185</t>
+          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-600-x-400-mm-weiss</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>21.18</v>
+        <v>33.5</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -4733,7 +4853,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="3" t="n">
-        <v>21.18</v>
+        <v>33.5</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
@@ -4742,7 +4862,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Polyethylene instead of PP; gross 25.42</t>
+          <t>18 mm thick instead of 20 mm</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -4753,39 +4873,39 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Jungheinrich PROFISHOP Austria</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Stalgast Pizzaballenbehälter aus Polypropylen 600x400x100 mm</t>
+          <t>Bartscher Schneidbrett 60x40 W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>Bartscher</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-pizzaballenbehaelter-aus-polypropylen-600x400x100-mm-bxtxh-929478-349074/</t>
+          <t>https://www.gastroladen.at/2310@A120592/Bartscher-Schneidbrett-60x40-W.htm</t>
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>28.9</v>
+        <v>34.9</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -4793,16 +4913,16 @@
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="3" t="n">
-        <v>28.9</v>
+        <v>29.08</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Title says polypropylene; spec table says 'Polyethylen (PE)' (conflicting)</t>
+          <t>PE, 16 mm plate (20 mm incl. feet), HACCP white</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -4813,35 +4933,35 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x100 mm, PP</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Teigwanne - weiß - rechteckig - 60,0 x 40,0 x 9,5 cm - Inhalt 18 l - Polyethylen</t>
+          <t>Schneidbrett Polyethylen weiß mit Saftrille 600 x 400 mm</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/teigwanne-weiss-rechteckig-60-0-x-40-0-x-9-5-cm-inhalt-18-l-polyethylen/202172-C</t>
+          <t>https://www.intergastro.at/schneidbrett-polyethylen-weiss-mit-saftrille-600-mm-x-400-mm-159019</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>11</v>
+        <v>35.05</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -4853,16 +4973,16 @@
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="3" t="n">
-        <v>11</v>
+        <v>35.05</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>95 mm high and polyethylene (vs 100 mm PP); regular price 17.10</t>
+          <t>20 mm thick, with juice groove; gross 42.06</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -4873,35 +4993,35 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>HACCP cutting board PE 600x400x20 mm</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>APS Deckel zu Pizzaballenbehälter</t>
+          <t>Stalgast Schneidbrett, HACCP, Farbe weiß, 600 x 400 x 18 mm</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/aps-deckel-zu-pizzaballenbehaelter-aps82441</t>
+          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-haccp-farbe-weiss-600-x-400-x-18-mm-bxtxh-928737-348334/</t>
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>8.99</v>
+        <v>27.9</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -4913,16 +5033,16 @@
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="3" t="n">
-        <v>8.99</v>
+        <v>27.9</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>PE, 600x400x10 mm; min. qty 2</t>
+          <t>18 mm instead of 20 mm; material PP (not PE); blue/yellow/green/brown 28.90</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4933,35 +5053,35 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Contacto Deckel zu Pizzaballenbehälter 600 x 400 mm</t>
+          <t>Schneidbrett GN 1/2 - 32,5 x 26,5 x 1,2 cm - HDPE weiß</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-deckel-zu-pizzaballenbehaelter-fuer-2510</t>
+          <t>https://www.gastro-hero.at/products/schneidbrett-gn-1-2-32-5-x-26-5-x-1-2-cm-hdpe-weiss</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>8</v>
+        <v>24.99</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -4973,16 +5093,16 @@
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="3" t="n">
-        <v>8</v>
+        <v>24.99</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>HD-polyethylene; sale price, normal 10.00</t>
+          <t>325x265x12 mm (GN 1/2) vs 300x200x10; no 300x200 board found</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4993,39 +5113,39 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble Deckel für stapelbare Pizzateigbehälter 60x40cm</t>
+          <t>Hendi Schneidbrett mit Griff, Weiß, 300x200mm</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/x1090@GN-GN539/Gastronoble-Deckel-f%C3%BCr-stapelbare-Pizzateigbeh%C3%A4lter-60x40cm.htm</t>
+          <t>https://www.gastrodax.de/hendi-schneidbrett-mit-griff-weiss-300-x-200-mm</t>
         </is>
       </c>
       <c r="G70" s="3" t="n">
-        <v>27.39</v>
+        <v>15.76</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -5033,7 +5153,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="3" t="n">
-        <v>22.83</v>
+        <v>15.76</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
@@ -5042,7 +5162,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>PE lid</t>
+          <t>300x200x10 mm HDPE, with handle</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5053,39 +5173,39 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Deckel für Pizzaballenbehälter, PP, 60 x 40 x 2 cm</t>
+          <t>Hygiplas HDPE kleines Schneidebrett weiß 300x225x12mm</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Hygiplas</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/deckel-fuer-pizzaballenbehaelter-art-967927-pp-60-x-40-x-2-cm-967928</t>
+          <t>https://www.gastroladen.at/2310@GN-HC867/Hygiplas-HDPE-kleines-Schneidebrett-wei%C3%9F-300x-225x12mm.htm</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>7.95</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
@@ -5093,16 +5213,16 @@
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="3" t="n">
-        <v>7.95</v>
+        <v>7.41</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Gross 9.54</t>
+          <t>300x225x12 mm vs 300x200x10</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5113,35 +5233,35 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Lid for 600x400 dough box</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Deckel - für Teigwanne (202180) - weiß - 60,0 x 40,0 x 3,5 cm - Polypropylen</t>
+          <t>Schneidbrett Polyethylen weiß 300 x 200 mm H 15 mm</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/deckel-fuer-teigwanne-202180-weiss-rechteckig-60-0-x-40-0-x-3-5-cm-polypropylen/202181-C</t>
+          <t>https://www.intergastro.at/schneidbrett-polyethylen-weiss-300-mm-x-200-mm-h-15-mm-158986</t>
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>16</v>
+        <v>8.74</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -5153,16 +5273,16 @@
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="3" t="n">
-        <v>16</v>
+        <v>8.74</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>PP lid 600x400; regular price 25.10</t>
+          <t>15 mm thick instead of 10 mm; gross 10.49</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5173,35 +5293,35 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>HACCP cutting board PE 300x200x10 mm</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>AmerBox Pizzaballenbox 60 x 40 x 7,5 cm</t>
+          <t>Stalgast Schneidbrett, rutschfest 270x190x9 mm, schwarz</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>AmerBox</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-7-5-cm.html</t>
+          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-rutschfest-270x190x9-mm-schwarz-928715-348311/</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>12.8</v>
+        <v>16.3</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -5213,16 +5333,16 @@
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="3" t="n">
-        <v>12.8</v>
+        <v>16.3</v>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>APPROX</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Polyethylene, 14 l</t>
+          <t>270x190x9 mm, black non-slip board, not HACCP colour-coded</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5233,35 +5353,35 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Pizzaballenbehälter, weiß Polyethylen, 60x40x7,5cm</t>
+          <t>AmerBox Pizzaballenbox 60 x 40 x 9,5 cm</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>AmerBox</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/pizzaballenbehaelter-weiss-polyethylen-60x40x75cm-2510600</t>
+          <t>https://www.allpax.at/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-9-5-cm.html</t>
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>33.59</v>
+        <v>13.95</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -5273,16 +5393,16 @@
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="3" t="n">
-        <v>33.59</v>
+        <v>13.95</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Sale price (normal 38.09). APS 600x400x75 box (material not stated) 10.79, min. qty 2</t>
+          <t>95 mm high and polyethylene (vs 100 mm PP), 18 l</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5293,35 +5413,35 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Contacto Pizzaballenbehälter 60 cm / 40 cm (600x400x75 mm)</t>
+          <t>9-tlg Teigbehälter-Set - 8 Behälter &amp; 1 Deckel - EN 600x400 - Höhe: 100mm - Polypropylen</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-pizzaballenbehaelter-60-cm-40-cm</t>
+          <t>https://www.ggmgastro.com/de-at-eur/9-tlg-teigbehaelter-set-8-behaelter-und-1-deckel-en-600x400-hoehe-100mm-polypropylen-weiss-tbpp6410</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -5329,11 +5449,15 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>8 boxes + 1 lid</t>
+        </is>
+      </c>
       <c r="K75" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>11.12</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
@@ -5342,7 +5466,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Polypropylene instead of PE; sale price, normal 12.35. Hendi 600x400x75 (material not stated) 19.43</t>
+          <t>Only sold as a set of 8 boxes plus 1 lid; net per box includes a share of the lid</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5353,39 +5477,39 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble Stapelbarer Pizzateigbehälter 7,5cm (60x40)</t>
+          <t>Pizzateigbox 18 l 600x400x95 mm</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Gastronoble</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/x1090@GN-GN536/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-7-5cm.htm</t>
+          <t>https://www.gastro-hero.at/products/pizzateigbox-18-l-600x400x95-mm</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>31.9</v>
+        <v>28.49</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -5393,16 +5517,16 @@
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="3" t="n">
-        <v>26.58</v>
+        <v>28.49</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>95 mm high; material PET (not PP)</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -5413,35 +5537,35 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Teigbehälter / Pizzaballenbehälter 14 ltr 600 x 400 mm H 75 mm (Polyethylen)</t>
+          <t>Hendi Pizzateigbox 600x400, AmerBox, Kitchen Line, 18L, 600x400x(H)95mm</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/teigbehaelter-pizzaballenbehaelter-14-ltr-600-mm-x-400-mm-h-75-mm-985534</t>
+          <t>https://www.gastrodax.de/hendi-pizzateig-box-kitchen-line-18-l-600-x-400-x-h-95-mm</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>21.38</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -5453,16 +5577,16 @@
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>21.38</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Gross 11.96</t>
+          <t>95 mm instead of 100 mm; material not stated</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -5473,39 +5597,39 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Jungheinrich PROFISHOP Austria</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Stalgast Pizzaballenbehälter aus Polypropylen 600 x 400 x 70 mm</t>
+          <t>Gastronoble Stapelbarer Pizzateigbehälter 9,5cm (60x40)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>https://www.jh-profishop.at/p/stalgast-pizzaballenbehaelter-aus-polypropylen-600-x-400-x-70-mm-bxtxh-929475-349073/</t>
+          <t>https://www.gastroladen.at/x1090@GN-GN537/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-9-5cm.htm</t>
         </is>
       </c>
       <c r="G78" s="3" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
@@ -5513,7 +5637,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="3" t="n">
-        <v>34.9</v>
+        <v>26.58</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -5522,7 +5646,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>70 mm instead of 75 mm; PP per title (spec asks PE)</t>
+          <t>95 mm high and polyethylene (vs 100 mm PP)</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -5533,35 +5657,35 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Pizza dough box 600x400x75 mm, PE</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Teig- und Pizzaballenbehälter - weiß - 60,0 x 40,0 x 7,5 cm - Inhalt 14 l - Polyethylen</t>
+          <t>Pizzaballenbehälter, Polyethylen 600x400x100 mm</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/teig-und-pizzaballenbehaelter-weiss-60-0-x-40-0-x-7-5-cm-inhalt-14-l-polyethylen/82440-B</t>
+          <t>https://www.intergastro.at/pizzaballenbehaelter-polyethylen-600x400x100-mm-bxtxh-1027185</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>21.18</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -5573,16 +5697,16 @@
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>21.18</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Regular price 12.00; Schneider 202170-C same spec 9.50</t>
+          <t>Polyethylene instead of PP; gross 25.42</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -5593,35 +5717,35 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Hendi Thermobox für GN 1/1</t>
+          <t>Stalgast Pizzaballenbehälter aus Polypropylen 600x400x100 mm</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/Hendi-Thermobox-fuer-GN-1-1.html</t>
+          <t>https://www.jh-profishop.at/p/stalgast-pizzaballenbehaelter-aus-polypropylen-600x400x100-mm-bxtxh-929478-349074/</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>284</v>
+        <v>28.9</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -5633,16 +5757,16 @@
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="3" t="n">
-        <v>284</v>
+        <v>28.9</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Front-loading LDPE box with rails, 477x680x620 mm; inner 335x533x590 mm (~105 l, above 80-90 l)</t>
+          <t>Title says polypropylene; spec table says 'Polyethylen (PE)' (conflicting)</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -5653,35 +5777,35 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Pizza dough box 600x400x100 mm, PP</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Thermobox ECO GN 1/1 - Frontlader (90 l)</t>
+          <t>Teigwanne - weiß - rechteckig - 60,0 x 40,0 x 9,5 cm - Inhalt 18 l - Polyethylen</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>GastroHero</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/thermobox-eco-gn-1-1-frontlader-thbe90</t>
+          <t>https://shopbuero.com/teigwanne-weiss-rechteckig-60-0-x-40-0-x-9-5-cm-inhalt-18-l-polyethylen/202172-C</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>169.9</v>
+        <v>11</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5817,16 @@
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="3" t="n">
-        <v>169.9</v>
+        <v>11</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>EXACT</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>90 l, 652x445x646 mm; sale price (normal 349.00)</t>
+          <t>95 mm high and polyethylene (vs 100 mm PP); regular price 17.10</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -5713,35 +5837,35 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Contacto Thermobox GN 1/1 Frontlader, 12 Auflageschienen</t>
+          <t>APS Deckel zu Pizzaballenbehälter</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Contacto</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/contacto-thermobox-gn-1-1-1</t>
+          <t>https://www.gastro-hero.at/products/aps-deckel-zu-pizzaballenbehaelter-aps82441</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>229.14</v>
+        <v>8.99</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -5753,16 +5877,16 @@
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="3" t="n">
-        <v>229.14</v>
+        <v>8.99</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Front loader GN 1/1, 495x635x630 mm outside; volume not stated; sale price, normal 342.00</t>
+          <t>PE, 600x400x10 mm; min. qty 2</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -5773,39 +5897,39 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Cambro isolierter Frontlader Lebensmitteltransportbehälter 86L</t>
+          <t>Contacto Deckel zu Pizzaballenbehälter 600 x 400 mm</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/0860@GN-DW565/Cambro-isolierter-Frontlader-Lebensmitteltransportbeh%C3%A4lter-86L.htm</t>
+          <t>https://www.gastrodax.de/contacto-deckel-zu-pizzaballenbehaelter-fuer-2510</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>305.9</v>
+        <v>8</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -5813,7 +5937,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="3" t="n">
-        <v>254.92</v>
+        <v>8</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
@@ -5822,7 +5946,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>For 4 x GN 1/1 100 mm; freight 90 EUR; currently out of stock. Thermo Future 93 l front-loader 226.90</t>
+          <t>HD-polyethylene; sale price, normal 10.00</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -5833,39 +5957,39 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Box COMBI schwarz, 12 Einschübe, 83 ltr, 630 x 500 x 580 mm</t>
+          <t>Gastronoble Deckel für stapelbare Pizzateigbehälter 60x40cm</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Thermohauser</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/box-combi-schwarz-12-einschuebe-83-ltr-630-mm-x-500-mm-h-580-mm-305715</t>
+          <t>https://www.gastroladen.at/x1090@GN-GN539/Gastronoble-Deckel-f%C3%BCr-stapelbare-Pizzateigbeh%C3%A4lter-60x40cm.htm</t>
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>265.95</v>
+        <v>27.39</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -5873,7 +5997,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="3" t="n">
-        <v>265.95</v>
+        <v>22.83</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
@@ -5882,7 +6006,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Front-loader category; also Schneider Front-Box GN 1/1 91 l at 218.07 net</t>
+          <t>PE lid</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -5893,35 +6017,35 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+          <t>Lid for 600x400 dough box</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>FRONT-BOX - 62,8 x 44,5 x 62,5 cm - Inhalt 91 l - GN 1/1 - EPP</t>
+          <t>Deckel für Pizzaballenbehälter, PP, 60 x 40 x 2 cm</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>WAS Germany</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/front-box-62-8-x-44-5-x-62-5-cm-inhalt-91-l-gn-1-1-epp/620660-C</t>
+          <t>https://www.intergastro.at/deckel-fuer-pizzaballenbehaelter-art-967927-pp-60-x-40-x-2-cm-967928</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>196</v>
+        <v>7.95</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -5933,16 +6057,16 @@
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="3" t="n">
-        <v>196</v>
+        <v>7.95</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>91 l (slightly above 80-90 l), EPP front loader; regular price 318.75</t>
+          <t>Gross 9.54</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -5953,31 +6077,35 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Lid for 600x400 dough box</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Deckel - für Teigwanne (202180) - weiß - 60,0 x 40,0 x 3,5 cm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/deckel-fuer-teigwanne-202180-weiss-rechteckig-60-0-x-40-0-x-3-5-cm-polypropylen/202181-C</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
         <v>16</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>ALLPAX Österreich</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>EN Tablett, Serie Tray 97, 53x37 cm</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.allpax.at/product_info.php/info/EN-Tablett.html</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>19.22</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -5989,16 +6117,16 @@
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="3" t="n">
-        <v>19.22</v>
+        <v>16</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Right size but fibreglass-reinforced polyester, not ABS/PP</t>
+          <t>PP lid 600x400; regular price 25.10</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6009,35 +6137,35 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany Tablett PP - GN 1/1, lichtgrau</t>
+          <t>AmerBox Pizzaballenbox 60 x 40 x 7,5 cm</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>AmerBox</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/was-germany-tablett-pp-gn-11-lichtgrau-9283530</t>
+          <t>https://www.allpax.at/product_info.php/info/AmerBox-Pizzaballenbox-60-x-40-x-7-5-cm.html</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>6.79</v>
+        <v>12.8</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -6049,16 +6177,16 @@
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="3" t="n">
-        <v>6.79</v>
+        <v>12.8</v>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>PP but GN 1/1 size 530x325 (not 370x530); sale price (normal 7.39). WAS polyester EN 53x37 tray 12.29</t>
+          <t>Polyethylene, 14 l</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6069,35 +6197,35 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Hendi Serviertablett, rechteckig, Euronorm, 370x530mm</t>
+          <t>(8 Stück) Teigbehälter - EN 600x400 - Weiß (70 mm)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/hendi-serviertablett-rechteckig-euronorm-370-x-530-mm</t>
+          <t>https://www.ggmgastro.com/de-at-eur/8-stueck-teigbehaelter-en-600x400-weiss-tbp647</t>
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>15.25</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -6105,11 +6233,15 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>set of 8</t>
+        </is>
+      </c>
       <c r="K88" s="3" t="n">
-        <v>15.25</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
@@ -6118,7 +6250,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Exact size; material not stated on page</t>
+          <t>70 mm high, polypropylene (vs 75 mm PE)</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6129,39 +6261,39 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>GastroHero Österreich</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Kristallon Serviertablett antirutsch 51 x 38cm</t>
+          <t>Pizzaballenbehälter, weiß Polyethylen, 60x40x7,5cm</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Kristallon</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/G16801@GN-C560/Kristallon-Serviertablett-antirutsch-51-x-38cm.htm</t>
+          <t>https://www.gastro-hero.at/products/pizzaballenbehaelter-weiss-polyethylen-60x40x75cm-2510600</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>8.98</v>
+        <v>33.59</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
@@ -6169,16 +6301,16 @@
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="3" t="n">
-        <v>7.48</v>
+        <v>33.59</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>510x380 mm, plastic (type not specified), non-slip</t>
+          <t>Sale price (normal 38.09). APS 600x400x75 box (material not stated) 10.79, min. qty 2</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6189,35 +6321,35 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>Gastrodax</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Tablett Polyester titanfarben rechteckig 530 x 370 mm</t>
+          <t>Contacto Pizzaballenbehälter 60 cm / 40 cm (600x400x75 mm)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>Contacto</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/tablett-polyester-titanfarben-rechteckig-530-mm-x-370-mm-396106</t>
+          <t>https://www.gastrodax.de/contacto-pizzaballenbehaelter-60-cm-40-cm</t>
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>18.19</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -6229,16 +6361,16 @@
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="3" t="n">
-        <v>18.19</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Right size but polyester/fibreglass, not ABS/PP; no ABS/PP tray of this size found</t>
+          <t>Polypropylene instead of PE; sale price, normal 12.35. Hendi 600x400x75 (material not stated) 19.43</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -6249,39 +6381,39 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>shopbuero.com</t>
+          <t>Gastroladen.at (Harotec GmbH)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Euronorm-Tablett - Stapelnocken - Serie 9605 - lichtgrau - 53 x 37 cm - Polyester</t>
+          <t>Gastronoble Stapelbarer Pizzateigbehälter 7,5cm (60x40)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>WAS Germany</t>
+          <t>Gastronoble</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>https://shopbuero.com/euronorm-tablett-stapelnocken-serie-9605-lichtgrau-53-x-37-cm-polyester/9605531-A</t>
+          <t>https://www.gastroladen.at/x1090@GN-GN536/Gastronoble-Stapelbarer-Pizzateigbeh%C3%A4lter-7-5cm.htm</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>11.9</v>
+        <v>31.9</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>excl.</t>
+          <t>incl.</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
@@ -6289,16 +6421,16 @@
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="3" t="n">
-        <v>11.9</v>
+        <v>26.58</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Right size but polyester (not ABS/PP); PP non-slip tray 46x36 cm 6.10; regular price 17.50</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -6309,35 +6441,35 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich</t>
+          <t>Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Thermo-Tablett rechteckig 5-teilig 430x290x(H)150 mm</t>
+          <t>Teigbehälter / Pizzaballenbehälter 14 ltr 600 x 400 mm H 75 mm (Polyethylen)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Hendi</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>https://www.allpax.at/product_info.php/info/Thermo-Tablett-rechteckig.html</t>
+          <t>https://www.intergastro.at/teigbehaelter-pizzaballenbehaelter-14-ltr-600-mm-x-400-mm-h-75-mm-985534</t>
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>36.09</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -6349,16 +6481,16 @@
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="3" t="n">
-        <v>36.09</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>5-piece set (ABS base, stainless tray, transparent hood, 2 cooling packs); 5 parts rather than 5 compartments</t>
+          <t>Gross 11.96</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -6369,35 +6501,35 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich</t>
+          <t>Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>APS Thermo-Set 5-tlg. ca. Ø 38 cm, Höhe 24 cm</t>
+          <t>Stalgast Pizzaballenbehälter aus Polypropylen 600 x 400 x 70 mm</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastro-hero.at/products/aps-thermo-set-5-tlg-ca-38-cm-hoehe-24-cm-aps09082</t>
+          <t>https://www.jh-profishop.at/p/stalgast-pizzaballenbehaelter-aus-polypropylen-600-x-400-x-70-mm-bxtxh-929475-349073/</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>46.9</v>
+        <v>34.9</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -6409,16 +6541,16 @@
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="3" t="n">
-        <v>46.9</v>
+        <v>34.9</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Round 5-piece set (stainless bowl, tray, roll-top hood, 2 cooling packs); not a compartment tray; min. qty 2</t>
+          <t>70 mm instead of 75 mm; PP per title (spec asks PE)</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -6429,21 +6561,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Pizza dough box 600x400x75 mm, PE</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Gastrodax</t>
+          <t>shopbuero.com</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>APS Thermo Tablett Set rechteckig (5-teilig)</t>
+          <t>Teig- und Pizzaballenbehälter - weiß - 60,0 x 40,0 x 7,5 cm - Inhalt 14 l - Polyethylen</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -6453,11 +6585,11 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrodax.de/aps-thermo-tablett-set-rechteckig</t>
+          <t>https://shopbuero.com/teig-und-pizzaballenbehaelter-weiss-60-0-x-40-0-x-7-5-cm-inhalt-14-l-polyethylen/82440-B</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>26.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -6469,16 +6601,16 @@
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="3" t="n">
-        <v>26.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>EXACT</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>5-piece set: insulated plastic base, stainless tray, PS lid, 2 cooling packs; 430x290x140 mm; 5 parts rather than 5 compartments</t>
+          <t>Regular price 12.00; Schneider 202170-C same spec 9.50</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -6489,39 +6621,39 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Gastroladen.at (Harotec GmbH)</t>
+          <t>ALLPAX Österreich</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Cambro Tablotherm Isolierte Schale mit Porzellantellern 37 x 53 x 10,5 cm</t>
+          <t>Hendi Thermobox für GN 1/1</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>Hendi</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastroladen.at/0860@GN-CJ645/Cambro-Tablotherm-Isolierte-Schale-mit-Porzellantellern-37-x-53-x-10-5-cm.htm</t>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-Thermobox-fuer-GN-1-1.html</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>256.9</v>
+        <v>284</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>incl.</t>
+          <t>excl.</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
@@ -6529,16 +6661,16 @@
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="3" t="n">
-        <v>214.08</v>
+        <v>284</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>APPROX</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Insulated tray with porcelain 2-compartment plate + 3 bowls with lids; not a simple 5-6 compartment thermo tray</t>
+          <t>Front-loading LDPE box with rails, 477x680x620 mm; inner 335x533x590 mm (~105 l, above 80-90 l)</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -6549,35 +6681,35 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Intergastro (AT shop)</t>
+          <t>GGM Gastro (Austrian storefront)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Tablett TABLOTHERM EURONORM isoliert mit Geschirr, Deckel, Pellet</t>
+          <t>Porter - Frontlader - 83 Liter - für 12x GN 1/1</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Cambro</t>
+          <t>GGM</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>https://www.intergastro.at/tablett-tablotherm-euronorm-isoliert-mit-geschirr-deckel-pellet-325159</t>
+          <t>https://www.ggmgastro.com/de-at-eur/porter-frontlader-83-liter-fuer-12x-gn-1-1-plb-300</t>
         </is>
       </c>
       <c r="G96" s="3" t="n">
-        <v>176.33</v>
+        <v>289.99</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -6589,19 +6721,1099 @@
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="3" t="n">
+        <v>289.99</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>PP, 83 l. Cheaper PU 'Thermobox Frontlader 92 l' (tpbe92): 127.99 net</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>RIEBER thermoport K 1000 unbeheizt-orange</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Rieber</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/rieberthermoportk1000unbeheizt-orange/</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>561</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="3" t="n">
+        <v>561</v>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Premium PP front-loader for GN 1/1 (12 rail pairs), unheated; volume not stated on the page. K 6000 front-loader 472.00 net</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Thermobox ECO GN 1/1 - Frontlader (90 l)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/thermobox-eco-gn-1-1-frontlader-thbe90</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="3" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>90 l, 652x445x646 mm; sale price (normal 349.00)</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Contacto Thermobox GN 1/1 Frontlader, 12 Auflageschienen</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/contacto-thermobox-gn-1-1-1</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>229.14</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="3" t="n">
+        <v>229.14</v>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Front loader GN 1/1, 495x635x630 mm outside; volume not stated; sale price, normal 342.00</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Cambro isolierter Frontlader Lebensmitteltransportbehälter 86L</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/0860@GN-DW565/Cambro-isolierter-Frontlader-Lebensmitteltransportbeh%C3%A4lter-86L.htm</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="3" t="n">
+        <v>254.92</v>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>For 4 x GN 1/1 100 mm; freight 90 EUR; currently out of stock. Thermo Future 93 l front-loader 226.90</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Box COMBI schwarz, 12 Einschübe, 83 ltr, 630 x 500 x 580 mm</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Thermohauser</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/box-combi-schwarz-12-einschuebe-83-ltr-630-mm-x-500-mm-h-580-mm-305715</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>265.95</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="3" t="n">
+        <v>265.95</v>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Front-loader category; also Schneider Front-Box GN 1/1 91 l at 218.07 net</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Front-loading insulated thermobox for GN 1/1 (~80-90 l)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>FRONT-BOX - 62,8 x 44,5 x 62,5 cm - Inhalt 91 l - GN 1/1 - EPP</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/front-box-62-8-x-44-5-x-62-5-cm-inhalt-91-l-gn-1-1-epp/620660-C</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>91 l (slightly above 80-90 l), EPP front loader; regular price 318.75</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>EN Tablett, Serie Tray 97, 53x37 cm</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/EN-Tablett.html</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="3" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Right size but fibreglass-reinforced polyester, not ABS/PP</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>(6 Stück) FAST FOOD Tablett - GN 1/1 - Polypropylen - Höhe 20mm - Schwarz</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-fast-food-tablett-gn-1-1-polypropylen-hoehe-20mm-schwarz-00553-6</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>PP but GN 1/1 size (530x325), not 530x370. Cambro fibreglass 530x370 tray: 199.99 per 12</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany Tablett PP - GN 1/1, lichtgrau</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/was-germany-tablett-pp-gn-11-lichtgrau-9283530</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="3" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>PP but GN 1/1 size 530x325 (not 370x530); sale price (normal 7.39). WAS polyester EN 53x37 tray 12.29</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Serviertablett, rechteckig, Euronorm, 370x530mm</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-serviertablett-rechteckig-euronorm-370-x-530-mm</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="3" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Exact size; material not stated on page</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Kristallon Serviertablett antirutsch 51 x 38cm</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Kristallon</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/G16801@GN-C560/Kristallon-Serviertablett-antirutsch-51-x-38cm.htm</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="3" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>510x380 mm, plastic (type not specified), non-slip</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Tablett Polyester titanfarben rechteckig 530 x 370 mm</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/tablett-polyester-titanfarben-rechteckig-530-mm-x-370-mm-396106</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="3" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Right size but polyester/fibreglass, not ABS/PP; no ABS/PP tray of this size found</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Service tray approx. 370x530 mm, ABS/PP</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Euronorm-Tablett - Stapelnocken - Serie 9605 - lichtgrau - 53 x 37 cm - Polyester</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/euronorm-tablett-stapelnocken-serie-9605-lichtgrau-53-x-37-cm-polyester/9605531-A</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Right size but polyester (not ABS/PP); PP non-slip tray 46x36 cm 6.10; regular price 17.50</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Thermo-Tablett rechteckig 5-teilig 430x290x(H)150 mm</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Thermo-Tablett-rechteckig.html</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="3" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>5-piece set (ABS base, stainless tray, transparent hood, 2 cooling packs); 5 parts rather than 5 compartments</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>APS Thermo-Set 5-tlg. ca. Ø 38 cm, Höhe 24 cm</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/aps-thermo-set-5-tlg-ca-38-cm-hoehe-24-cm-aps09082</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Round 5-piece set (stainless bowl, tray, roll-top hood, 2 cooling packs); not a compartment tray; min. qty 2</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>APS Thermo Tablett Set rechteckig (5-teilig)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/aps-thermo-tablett-set-rechteckig</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="3" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>5-piece set: insulated plastic base, stainless tray, PS lid, 2 cooling packs; 430x290x140 mm; 5 parts rather than 5 compartments</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Tablotherm Isolierte Schale mit Porzellantellern 37 x 53 x 10,5 cm</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/0860@GN-CJ645/Cambro-Tablotherm-Isolierte-Schale-mit-Porzellantellern-37-x-53-x-10-5-cm.htm</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="3" t="n">
+        <v>214.08</v>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>Insulated tray with porcelain 2-compartment plate + 3 bowls with lids; not a simple 5-6 compartment thermo tray</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Insulated thermo tray with lid, 5-6 compartments</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Tablett TABLOTHERM EURONORM isoliert mit Geschirr, Deckel, Pellet</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/tablett-tablotherm-euronorm-isoliert-mit-geschirr-deckel-pellet-325159</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
         <v>176.33</v>
       </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="3" t="n">
+        <v>176.33</v>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>APPROX</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>Insulated PP tray system incl. dishes, lid and heat pellet; not a simple 5-6 compartment thermo tray</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
@@ -6683,20 +7895,20 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10.41</v>
+        <v>7.83</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>14.07</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>22.43</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+          <t>GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -6713,24 +7925,24 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>7.29</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10.08</v>
+        <v>10.17</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18.75</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+          <t>ALLPAX Österreich, Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -6743,20 +7955,20 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.5</v>
+        <v>3.33</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>12</v>
+        <v>7.91</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+          <t>GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
@@ -6773,20 +7985,20 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5</v>
+        <v>2.46</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9.24</v>
+        <v>7.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>16.66</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+          <t>GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -6803,20 +8015,20 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1.42</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.89</v>
+        <v>4.33</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -6833,20 +8045,20 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>1.95</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.16</v>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
+          <t>GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
@@ -6883,20 +8095,20 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>19.76</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>30.62</v>
+        <v>30.5</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>93.66</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
@@ -6913,20 +8125,20 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>18</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>23.9</v>
+        <v>24.23</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>33.69</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -6943,20 +8155,20 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>34.27</v>
+        <v>33.5</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>49.39</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
@@ -7003,20 +8215,20 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>11</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>21.38</v>
+        <v>21.28</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -7063,20 +8275,20 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12.8</v>
+        <v>11.39</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>34.9</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -7093,24 +8305,24 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>169.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>242.03</v>
+        <v>254.92</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>284</v>
+        <v>289.99</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -7140,7 +8352,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -7208,7 +8420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7248,12 +8460,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GGM Gastro (Austrian storefront)</t>
+          <t>LUSINI Austria (incl. VEGA and PULSIVA)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.ggmgastro.com/de-at-eur</t>
+          <t>https://www.lusini.com/de-at/</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -7263,78 +8475,78 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Price not readable: product prices are filled in by JavaScript (page HTML only contains a '{{price}}' template); could not be read with the tools available.</t>
+          <t>Blocks automated access: every lusini.com page (including robots.txt and the sitemap) returns HTTP 403 to scripts and to the web-fetch tool, so no price could be read or verified. Re-checked 2026-09-30.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>B2B only; site states net prices incl. delivery. Search-engine snippets show pack prices (e.g. 6-pc GN sets), but these were not verified on the Austrian storefront, so none were recorded.</t>
+          <t>vega-direct.at and pulsiva.at now redirect to lusini.com/de-at, and vega-direct.com / pulsiva.com to lusini.com/vega and /pulsiva: VEGA and PULSIVA are sold through the LUSINI shop. Search-engine snippets show LUSINI de-at listings (e.g. pdp/248536 'Behälter GN 1/1'), but prices/variants could not be confirmed on the site, so none were recorded. Needs a manual check in a normal browser.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LUSINI (Austrian storefront)</t>
+          <t>METRO Austria</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://www.lusini.com/de-at/</t>
+          <t>https://shop.metro.at</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>pan-EU</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Site blocks automated access (HTTP 403), so no prices could be read or verified.</t>
+          <t>Login only: shop.metro.at redirects to the sign-in page ('Willkommen im METRO Shop' - customer registration required). www.metro.at returns HTTP 403 and produkte.metro.at is a JavaScript-only page with no readable product data.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Large pan-EU hotel &amp; gastro supplier; hotelwaesche.at redirects here.</t>
+          <t>Cash &amp; carry wholesaler; METRO Professional GN containers exist in its range (seen on metro.de marketplace and in Austrian flyer-aggregator sites), but no current Austrian online price is publicly readable.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Kaufland.at Marktplatz</t>
+          <t>HENDI Austria</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaufland.at</t>
+          <t>https://hendi.com/at</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>marketplace</t>
+          <t>pan-EU</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access (HTTP 403); prices not verified.</t>
+          <t>Price not readable: hendi.com/at product pages (3,467 AT URLs in the public sitemap) are JavaScript app shells - the HTML contains no product data or prices, and no HENDI AT prices appear in search indexes. HENDI sells through dealers.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gastro sellers such as GASTROVERTRIEBSKONTOR, getgastro and HENDI items are listed (per search-engine snippets).</t>
+          <t>HENDI products are priced at Gastro Star, GastroHero, Gastrodax and Allpax (see Prices sheet, brand = Hendi).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>eBay.at / Amazon.de</t>
+          <t>Kaufland.at Marktplatz</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.at</t>
+          <t>https://www.kaufland.at</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7344,37 +8556,41 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access (403 / bot check); prices not verified.</t>
+          <t>Blocks automated access (HTTP 403); prices not verified.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>amazon.at redirects to amazon.de.</t>
+          <t>Gastro sellers such as GASTROVERTRIEBSKONTOR, getgastro and HENDI items are listed (per search-engine snippets).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>METRO Österreich</t>
+          <t>eBay.at / Amazon.de</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.metro.at</t>
+          <t>https://www.ebay.at</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>marketplace</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access (HTTP 403). Cash &amp; carry wholesaler; online prices generally need a customer card/login.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>Blocks automated access (403 / bot check); prices not verified.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>amazon.at redirects to amazon.de.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7433,66 +8649,66 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Hendi Österreich</t>
+          <t>Gradwohl (gastroartikel.at)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://hendi.com/at</t>
+          <t>https://gastroartikel.at</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>pan-EU</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Manufacturer site that renders in JavaScript; no prices visible. Hendi sells through dealers.</t>
+          <t>Catalogue only, no prices: an Austrian manufacturer (Melk) that sells through dealers ('Shops finden').</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Hendi items are priced at Gastrodax, GastroHero and Allpax.</t>
+          <t>Makes Polyhygien cutting boards and kitchen tools.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Gradwohl (gastroartikel.at)</t>
+          <t>Stalgast</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://gastroartikel.at</t>
+          <t>https://www.stalgast.de</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>pan-EU</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Catalogue only, no prices: an Austrian manufacturer (Melk) that sells through dealers ('Shops finden').</t>
+          <t>Catalogue without prices on stalgast.de; stalgast.at redirects to the Swiss site (CHF).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Makes Polyhygien cutting boards and kitchen tools.</t>
+          <t>Stalgast items are priced at Jungheinrich PROFISHOP and Intergastro.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Stalgast</t>
+          <t>Esmeyer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.stalgast.de</t>
+          <t>https://www.esmeyer-shop.de</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7502,51 +8718,47 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Catalogue without prices on stalgast.de; stalgast.at redirects to the Swiss site (CHF).</t>
+          <t>Blocks automated access (HTTP 403); the fetched page showed no price. Not verified.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Stalgast items are priced at Jungheinrich PROFISHOP and Intergastro.</t>
+          <t>German gastro webshop.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Esmeyer</t>
+          <t>Gastrotiger</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.esmeyer-shop.de</t>
+          <t>https://gastrotiger.at</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>pan-EU</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access (HTTP 403); the fetched page showed no price. Not verified.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>German gastro webshop.</t>
-        </is>
-      </c>
+          <t>Blocks automated access (HTTP 403); not verified.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Gastrotiger</t>
+          <t>Gastro Zimml</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://gastrotiger.at</t>
+          <t>https://www.gastrozimml.at</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7556,20 +8768,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Blocks automated access (HTTP 403); not verified.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>Not counted: shows prices (excl. 20% VAT) but only a request basket ('Anfragekorb'), no checkout, and fewer than 6 basket items (only stainless sauce dispensers, no plastic GN, boards or bottles).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol (Oberlienz); HOGAST partner.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Gastro Zimml</t>
+          <t>OM Gastrohandel</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gastrozimml.at</t>
+          <t>https://om-gastrohandel.at</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7579,91 +8795,37 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Not counted: shows prices (excl. 20% VAT) but only a request basket ('Anfragekorb'), no checkout, and fewer than 6 basket items (only stainless sauce dispensers, no plastic GN, boards or bottles).</t>
+          <t>Not counted: shows prices (excl. VAT) but carries no basket items (focus on cleaning chemicals, paper and dishwashers).</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tyrol (Oberlienz); HOGAST partner.</t>
+          <t>Altendorf, Lower Austria.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>OM Gastrohandel</t>
+          <t>ZORRO Gastro (AT storefront)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://om-gastrohandel.at</t>
+          <t>https://www.zorro.de/at/</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>pan-EU</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Not counted: shows prices (excl. VAT) but carries no basket items (focus on cleaning chemicals, paper and dishwashers).</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Altendorf, Lower Austria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Gastro Star</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gastro-star.at</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Not counted: shows prices (excl. + incl. 20% VAT) but focuses on equipment; no plastic GN, boards, squeeze bottles or dough boxes found.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Only stainless/Rieber GN lids found.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ZORRO Gastro (AT storefront)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zorro.de/at/</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>pan-EU</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
           <t>Not counted: shows prices, but focuses on equipment; GN range is stainless steel only and none of the plastic basket items were found.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/research_AT.xlsx
+++ b/research_AT.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Basket items found (of 17, any match)</t>
+          <t>Basket items found (of 34, any match)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -922,14 +922,14 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Austrian B2B gastro equipment shop (WooCommerce). BELOW the 6-item threshold (5 items: plastic GN items from HENDI/RIEBER and Rieber front loaders only; no squeeze bottles, boards, dough boxes or trays in its catalogue). Included at the user's request; prices are counted in the Summary.</t>
+          <t>Austrian B2B gastro equipment shop (WooCommerce). Carries plastic GN containers/lids (HENDI, RIEBER) and Rieber front-loaders only - no squeeze bottles, cutting boards, dough boxes or trays. Original 17-item basket: 5 items (below the 6-item threshold); new variants 18-34: 8 items. Included at the user's request; prices are counted in the Summary.</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7819,6 +7819,6618 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Hendi HACCP Aufbewahrungsbehälter GN 1/1, 65 mm</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-HACCP-Aufbewahrungsbehaelter-GN-1-1-65-mm.html</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="3" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>PP, BPA-free, 9 l</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>(6 Stück) Polypropylen-Behälter GN 1/1 - Milchig - Höhe: 65mm</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-polypropylen-behaelter-gn-1-1-milchig-hoehe-65mm-gpp1165-6</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>RRP 83.99</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Hendi GN-Behälter mit Deckel und HACCP-Clips, GN 1/1, 65 mm, 8 L, PP</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/hendi-gn-behaelter-mit-deckel-und-haccp-clips-gn-11-65-mm-8-l-pp-873335</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+      <c r="K117" s="3" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Includes lid and HACCP clips</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Behälter 1/1, 9L, Transparent, 530x325x(H)65mm – Polypropylen</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-gn-1-1-9-l-transparent-530-x-325-x-h-65-mm</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="3" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Gastronormbehälter GN 1/1 x 65 mm GN 84 Polypropylen transparent</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gastronormbehaelter-gn-1-1-x-65-mm-gn-84-polypropylen-transparent-252104</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+      <c r="K119" s="3" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>Gross 9.76</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - Inhalt 9,0 l - GN 1/1 (530 x 325 mm) - 65 mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-inhalt-9-0-l-gn-1-1-530-x-325-mm-65-mm-polypropylen/530000-C</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 13.55</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>PC GN 1/3 Höhe 100 mm schwarz</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/PC-GN-1-3-Hoehe-100-mm-schwarz.html</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>'jetzt' price; regular 5.69</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>(12 Stück) Polycarbonat-Behälter GN 1/3 - Schwarz - Höhe: 100mm</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polycarbonat-behaelter-gn-1-3-schwarz-hoehe-100mm-gpcp13100s</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>65.98999999999999</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>RIEBER GN 1/3 Polycarbonat-Behälter - Tiefe 100mm</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Rieber</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/riebergn13polycarbonat-behaelter-tiefe100mm/</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+      <c r="K123" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>Gross 15.60</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Vogue GN-Behälter 1/3 Polycarbonat - Tiefe 100 mm</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/vogue-gn-behaelter-13-polycarbonat-tiefe-100-mm-u233</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="3" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>Sale price (normal 6.59); min. qty 4</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>B.PRO Gastronorm-Behälter 3,8 Liter Polycarbonat-GN 1/3 - 100 mm</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>B.PRO</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/b-pro-gastronorm-behaelter-3-8-liter-polycarbonat-gn-1-3-100-mm</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="3" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>Sale price (normal 17.10); Hendi PC GN 1/3 100 mm 20.93</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Camview BPA-freier GN 1/3 Behälter 100mm</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3020@GN-DW539/Cambro-Camview-BPA-freier-GN-1-3-Beh%C3%A4lter-100mm.htm</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="3" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>BPA-free Camview copolyester, not standard polycarbonate; Vogue PC GN 1/3 only offered in 65/150/200 mm</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Gastronorm Behälter GN 1/3 GN 96 BLACK Polycarbonat schwarz H 100 mm</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gastronorm-behaelter-gn-1-3-gn-96-black-polycarbonat-schwarz-h-100-mm-1016777</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Gastronormbehälter, Polycarbonat, GN 1/3 (100 mm)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-gastronormbehaelter-polycarbonat-gn-1-3-100-mm-928263-347758/</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>Black version 16.30</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - GN 1/3 (325 x 176 mm) - 100 mm - Inhalt 3,8 l - Polycarbonat</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-gn-1-3-325-x-176-mm-100-mm-inhalt-3-8-l-polycarbonat/530121-C</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 10.30</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>GN Behälter 1/2, 150 mm aus Kunststoff</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/GN-Behaelter-1-2-150-mm-aus-Kunststoff.html</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>Plastic type not stated; 'jetzt' price, regular 5.85</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>(12 Stück) Polypropylen-Behälter GN 1/2 - Milchig - Höhe: 150mm</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polypropylen-behaelter-gn-1-2-milchig-hoehe-150mm-gpp12150</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Polypropylen Behälter GN 1/2 – 325x265x150mm</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/polypropylenbehaeltergn12-325x265x150mm/</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>Gross 9.00</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Schneider PP GN 1/2 Behälter 150 mm, 9 l</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/schneider-pp-gn-12-behaelter-150-mm-9-l-530012</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>Min. qty 8</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Behälter 1/2, 9,5L, Transparent, 325x265x(H)150mm – Polypropylen</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-haccp-aufbewahrungsbehaelter-gn-1-2-9-5-l-transparent-325-x-265-x-h-150-mm</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="3" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Polypropylen GN 1/2 Behälter 150mm</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3030@GN-DW503/Cambro-Polypropylen-GN-1-2-Beh%C3%A4lter-150mm.htm</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="3" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>8.9 l</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>GN Behälter GN 1/2 x 150 mm Kunststoff</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gn-behaelter-gn-1-2-x-150-mm-kunststoff-253638</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>Plastic type not stated on page (APS PP line); the WAS GN 84 PP 1/2 150 mm is only a variant option of the 65 mm page and not separately priced</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast ARAVEN Gastronormbehälter mit Deckel, Polypropylen, GN 1/2 (150 mm)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast / Araven</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-araven-gastronormbehaelter-mit-deckel-polypropylen-gn-1-2-150-mm-928334-347849/</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Includes lid (container not sold separately)</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - BPA frei - Serie 84 - 9,0 l - GN 1/2 - 150 mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-bpa-frei-serie-84-inhalt-9-0-l-gn-1-2-325-x-265-mm-150-mm-polypropylen-premium-qualitaet/8412150-A</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 7.40</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>PC GN Deckel 1/1 schwarz</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/PC-GN-Deckel-1-1-schwarz.html</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="3" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Black PC; regular 9.29</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>(6 Stück) Polycarbonat-Deckel GN 1/1 - Höhe: 35mm</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-polycarbonat-deckel-gn-1-1-hoehe-35mm-82001-6</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>PC lid with 35 mm height (raised rather than flat standard lid)</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>RIEBER-Polycarbonat Flachdeckel für GN 1/1 Behälter</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Rieber</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/rieber-polycarbonatflachdeckelfuergn11behaelter/</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>Flat PC lid</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Vogue GN-Deckel 1/1 Polycarbonat</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/vogue-gn-deckel-11-polycarbonat-u244</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="3" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Sale price (normal 10.89); min. qty 4</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Deckel, GN 1/1, Polykarbonat transparent, 530 x 325 mm</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-gastronorm-deckel-gn-1-1-polykarbonat-transparent-530-x-325-mm</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="3" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Polycarbonat Deckel GN 1/1 mit Griff</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3020@GN-DM742/Cambro-Polycarbonat-Deckel-GN-1-1-mit-Griff.htm</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="3" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Flat PC lid with handle</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>GN Deckel GN 1/1 Polycarbonat transparent</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gn-deckel-gn-1-1-polycarbonat-transparent-252033</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="3" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>GN-Deckel - aufliegend - GN 1/1 (530 x 325 mm) - Polycarbonat</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-deckel-aufliegend-gn-1-1-530-x-325-mm-polycarbonat/530105-C</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 16.55</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>(12 Stück) Polypropylen-Behälter GN 1/6 - Milchig - Höhe: 100mm</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polypropylen-behaelter-gn-1-6-milchig-hoehe-100mm-gpp16100-12</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Polypropylen Behälter GN 1/6 – 176x162x100mm</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/polypropylenbehaeltergn16-176x162x100mm/</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Schneider PP GN 1/6 Behälter 100 mm, 1,6 l</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/schneider-pp-gn-16-behaelter-100-mm-16-l-530041</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="3" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>Min. qty 8</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Behälter 1/6, 1,6L, Transparent, 176x162x(H)100mm (HACCP-Aufbewahrungsbehälter)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-haccp-aufbewahrungsbehaelter-gn-1-6-1-6-l-transparent-176-x-162-x-h-100-mm</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="3" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>Hendi HACCP storage line, which is PP (the GN 1/3 sibling is labelled Polypropylen); this page does not state the material</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Polypropylen GN 1/6 Behälter 100mm</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3030@GN-DW508/Cambro-Polypropylen-GN-1-6-Beh%C3%A4lter-100mm.htm</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>1.5 l</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Gastronorm-Schale GN 1/6 x 100 mm Kunststoff transparent (Cambro PP)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gastronorm-schale-gn-1-6-x-100-mm-kunststoff-transparent-252808</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>Price per piece but sold in VPE of 6; APS GN 1/6 x 100 mm 'Kunststoff' 2.86</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Gastronormbehälter, Polypropylen, GN 1/6 (100 mm)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-gastronormbehaelter-polypropylen-gn-1-6-100-mm-928365-347888/</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - Inhalt 1,6 l - GN 1/6 (176 x 162 mm) - 100 mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-inhalt-1-6-l-gn-1-6-176-x-162-mm-100-mm-polypropylen/530041-C</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 4.25</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>(12 Stück) Polypropylen-Behälter GN 1/9 - Milchig - Höhe: 100mm</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polypropylen-behaelter-gn-1-9-milchig-hoehe-100mm-gpp19100-12</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Polypropylen Behälter GN 1/9 – 176x108x100mm</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/polypropylenbehaeltergn19-176x108x100mm/</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Hendi GN-Behälter mit Deckel und HACCP-Clips, GN 1/9, 100 mm, 1 L, PP</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/hendi-gn-behaelter-mit-deckel-und-haccp-clips-gn-19-100-mm-1-l-pp-873137</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>Includes lid and HACCP clips</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Behälter 1/9, 0,9L, Transparent, 176x108x(H)100mm (HACCP-Aufbewahrungsbehälter)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-haccp-aufbewahrungsbehaelter-gn-1-9-1-l-transparent-176-x-108-x-h-100-mm</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="3" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>Hendi HACCP storage line (PP); material not stated on this page</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Gastronorm-Schale GN 1/9 x 100 mm Kunststoff transparent (Cambro PP)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gastronorm-schale-gn-1-9-x-100-mm-kunststoff-transparent-252816</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>Price per piece, sold in VPE of 6</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast ARAVEN Gastronormbehälter mit Deckel, Polypropylen, GN 1/9 (100 mm)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast / Araven</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-araven-gastronormbehaelter-mit-deckel-polypropylen-gn-1-9-100-mm-928375-347898/</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>Includes lid</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - Inhalt 0,9 l - GN 1/9 (176 x 108 mm) - 100 mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-inhalt-0-9-l-gn-1-9-176-x-108-mm-100-mm-polypropylen/530051-C</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 3.30</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Quetschflasche in Transparent, 200 ml</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-Quetschflasche-in-Transparent-200-ml.html</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>200 ml (vs 250); plastic type not stated; cap</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Dosierflasche, weiß, 250 ml, Schraubdeckel und Verschlusskappe</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/dosierflasche-weiss-250-ml-schraubdeckel-und-verschlusskappe-1460251</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="3" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>Material not stated on page</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Contacto Quetschflasche 0,25 l</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/contacto-quetschflasche-0-25-l-1</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Polyethylene (not PP), screw cap with closure cap; sale price (normal 1.05)</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Vogue Quetschflasche klar 237ml</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/G16771B@GN-K062/Vogue-Quetschflasche-klar-237ml.htm</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>237 ml, polyethylene (not PP)</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Quetschflasche Kunststoff 250 ml weiß transluzent Schraubdeckel</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/quetschflasche-kunststoff-250-ml-weiss-transluzent-schraubdeckel-50-mm-h-190-mm-247045</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Polyethylene (not PP)</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Quetschflasche in Transparent, 700 ml</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-Quetschflasche-in-Transparent-700-ml.html</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>700 ml; plastic type not stated; cap</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>(6 Stück) Quetschflasche mit mittlerer Membran - 710ml</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-quetschflasche-mit-mittlerer-membran-710ml-ffo-004</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>710 ml, FIFO type with valve; material not stated</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Vogue Quetschflasche gelb 681ml</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/vogue-quetschflasche-gelb-681ml-k158</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>681 ml; material not stated on page; sale price (normal 1.69); min. qty 4</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Contacto Quetschflasche 0,7 l</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/contacto-quetschflasche-0-7-l-2</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>700 ml; polyethylene; sale price (normal 1.35). Same URL also lists a 2.56 variant</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Vogue Quetschflasche klar 681ml</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/G16771B@GN-K163/Vogue-Quetschflasche-klar-681ml.htm</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>681 ml, polyethylene (not PP)</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Quetschflasche 700 ml Kunststoff weiß transluzent Schraubdeckel</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/quetschflasche-700-ml-kunststoff-weiss-transluzent-schraubdeckel-65-mm-h-240-mm-247043</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>700 ml, polyethylene (not PP)</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Schneidebrett 45 x 30 cm in Rot</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-Schneidebrett-45-x-30-cm-in-Rot.html</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr"/>
+      <c r="K173" s="3" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>Red, 450x300x13 mm (vs 400x300x20)</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Schneidebrett - 250x400mm - HACCP-Konform - Rot</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/schneidebrett-250x400mm-haccp-konform-rot-sbp25r</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="3" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>Red HACCP board but 250x400 mm (vs 400x300)</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Schneidbrett 45 x 30 x 1,3 cm - HDPE rot</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/schneidbrett-45-x-30-x-1-3-cm-hdpe-rot</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr"/>
+      <c r="K175" s="3" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>Red HDPE but 450x300x13 mm (vs 400x300x20)</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Schneidbretter HACCP 450x300, Rot</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-450-x-300-mm-rot</t>
+        </is>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="3" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>Red, 450x300 mm (vs 400x300); thickness not checked</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Hygiplas standard Schneidebrett mit hoher Dichte rot 450x300x12mm</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Hygiplas</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/2310@GN-J010/Hygiplas-standard-Schneidebrett-mit-hoher-Dichte-rot.htm</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr"/>
+      <c r="K177" s="3" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>Red HDPE but 450x300x12 mm (vs 400x300x20)</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Schneidebrett rot HDPE 500, 400 mm x 300 mm</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Comas</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/schneidebrett-rot-hdpe-500-400-mm-x-300-mm-997227</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>Red HDPE; 20 mm per the series size list (400 x 300 x H 20 mm)</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Schneidbrett, HACCP, Farbe rot, 450 x 300 x 13 mm</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-haccp-farbe-rot-450-x-300-x-13-mm-bxtxh-928724-348321/</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>Red but 450x300x13 mm (vs 400x300x20)</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>9-tlg Teigbehälter-Set - 8 Behälter &amp; 1 Deckel - EN 600x400 - Höhe: 75mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/9-tlg-teigbehaelter-set-8-behaelter-und-1-deckel-en-600x400-hoehe-75mm-polypropylen-weiss-tbpp647</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>8 boxes + 1 lid</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>Only sold as set of 8 PP boxes plus 1 lid; net per box includes a share of the lid</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>WAS Pizzaballenbehälter 60 x 40 x 8 cm Polypropylen</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/was-pizzaballenbehaelter-60-x-40-x-8-cm-polypropylen</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>80 mm instead of 75 mm; PP; no lid</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Cambro Pizzateigkiste aus Polyethylen 60x40x7cm</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/G16888@GN-FS330/Cambro-Pizzateigkiste-aus-Polyethylen-60x40x7cm.htm</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="3" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>Polyethylene (not PP), 70 mm high; no lid</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Pizzaballenbehälter weiß 600 x 400 x 80 mm, PP</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/pizzaballenbehaelter-weiss-600-mm-x-400-mm-h-80-mm-967927</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="3" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>80 mm instead of 75 mm; PP; no lid. Contacto 600x400x75 (material not stated) 10.02</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Pizzaballenbehälter aus Polypropylen 600 x 400 x 70 mm</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-pizzaballenbehaelter-aus-polypropylen-600-x-400-x-70-mm-bxtxh-929475-349073/</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="3" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>70 mm instead of 75 mm; PP per title</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Teigwanne - ohne Deckel - 60,0 x 40,0 x 8,2 cm - 13 l - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/teigwanne-ohne-deckel-weiss-rechteckig-60-0-x-40-0-x-8-2-cm-inhalt-13-l-polypropylen/202180-C</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>82 mm instead of 75 mm; PP, no lid; regular price 28.20. APS PE 600x400x75: 8.80</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>PC GN 1/1 Höhe 100 mm schwarz</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/PC-GN-1-1-Hoehe-100-mm-schwarz.html</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>'jetzt' price; regular 9.09; available from week 49/2026</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>(6 Stück) Polycarbonat-Behälter GN 1/1 - Schwarz - Höhe: 100mm</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-polycarbonat-behaelter-gn-1-1-schwarz-hoehe-100mm-gpcp11100s</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>RIEBER GN 1/1 Polycarbonat-Behälter - Tiefe 100mm</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Rieber</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/riebergn11polycarbonat-behaelter-tiefe100mm/</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr"/>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Vogue GN-Behälter 1/1 Polycarbonat - Tiefe 100 mm</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/vogue-gn-behaelter-11-polycarbonat-tiefe-100-mm-u225</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="3" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>Sale price (normal 19.79); min. qty 4</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Behälter 1/1, 14L, Transparent, 530x325x(H)100mm (Polycarbonat)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-gn-1-1-14-l-polykarbonat-transparent-530-x-325-x-h-100-mm</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>Contacto PC GN 1/1 100 mm 16.72 (sale, normal 20.90)</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Vogue Polycarbonat GN-Behälter GN1/1 100mm</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3020@GN-U225/Vogue-Polycarbonat-GN-Beh%C3%A4lter-GN1-1-100mm.htm</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="3" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>Cambro PC GN 1/1 100 mm (DM729) 22.39</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Gastronorm Behälter GN 1/1 GN 96 BLACK Polycarbonat schwarz H 100 mm</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gastronorm-behaelter-gn-1-1-gn-96-black-polycarbonat-schwarz-h-100-mm-1016769</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="3" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - GN 1/1 (530 x 325 mm) - 100 mm - Inhalt 13,3 l - Polycarbonat</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-gn-1-1-530-x-325-mm-100-mm-inhalt-13-3-l-polycarbonat/530101-C</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 27.75</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>PC GN 1/6 Höhe 100 mm schwarz</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/PC-GN-1-6-Hoehe-100-mm-schwarz.html</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>Regular 4.59</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>(12 Stück) Polycarbonat-Behälter GN 1/6 - Transparent - Höhe: 100mm</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/12-stueck-polycarbonat-behaelter-gn-1-6-transparent-hoehe-100mm-gpcp16100</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J195" s="2" t="inlineStr">
+        <is>
+          <t>set of 12</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>RIEBER GN 1/6 Polycarbonat-Behälter - Tiefe 100mm</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Rieber</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/riebergn16polycarbonat-behaelter-tiefe100mm/</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Vogue GN-Behälter 1/6 Polycarbonat - Tiefe 100 mm</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/vogue-gn-behaelter-16-polycarbonat-tiefe-100-mm-u240</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="3" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>Sale price (normal 4.39); min. qty 4</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Gastronorm-Behälter 1/6, 1,6L, Transparent, 176x162x(H)100mm (Polycarbonat)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-gastronorm-behaelter-gn-1-6-1-6-l-polykarbonat-transparent-176-x-162-x-h-100-mm</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="3" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Vogue Polycarbonat GN-Behälter GN1/6 100mm</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Vogue</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3020@GN-U240/Vogue-Polycarbonat-GN-Beh%C3%A4lter-GN1-6-100mm.htm</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Gastronorm Behälter GN 1/6 GN 96 BLACK Polycarbonat schwarz H 100 mm</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gastronorm-behaelter-gn-1-6-gn-96-black-polycarbonat-schwarz-h-100-mm-1016785</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Gastronormbehälter, Polycarbonat, schwarz, GN 1/6 (100 mm)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-gastronormbehaelter-polycarbonat-schwarz-gn-1-6-100-mm-928314-347822/</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>GN-Behälter - GN 1/6 (176 x 162 mm) - 100 mm - Inhalt 1,6 l - Polycarbonat</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-behaelter-gn-1-6-176-x-162-mm-100-mm-inhalt-1-6-l-polycarbonat/530141-C</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 5.95</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Schneidebrett GN 1/1 in Rot</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-Schneidebrett-GN-1-1-in-Rot.html</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="3" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>Red 530x325, HACCP; thickness not stated; with juice groove</t>
+        </is>
+      </c>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Schneidebrett - 325x530mm - HACCP-Konform - Rot</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/schneidebrett-325x530mm-haccp-konform-rot-sbp53r</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="3" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>Red PE board; thickness not shown on this page (white board of same series is 325x530x20 mm)</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Hendi Schneidbrett HACCP Gastronorm 1/1, Rot, 530x325mm</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/hendi-schneidbretter-haccp-gastronorm-1-1-gn-1-1-rot-530-x-325-mm</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="3" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>530x325x15 mm, red; material not stated on page</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Bartscher Schneidbrett PRO 53x32 R-R (rot)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Bartscher</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/2310@A120513/Bartscher-Schneidbrett-PRO-53x32-R-R.htm</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="3" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>Red PE 530x325 but 20 mm plate (vs 15 mm), rubber feet, juice groove</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Schneidbrett Kunststoff rot mit Saftrille 530 x 325 mm H 20 mm</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Dick</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/schneidbrett-kunststoff-rot-mit-saftrille-530-mm-x-325-mm-h-20-mm-159103</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="3" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>20 mm instead of 15 mm, juice groove; premium brand (F. Dick)</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Schneidbrett, HACCP, Farbe rot, GN1/1, Stärke 15 mm</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-schneidbrett-haccp-farbe-rot-gn1-1-staerke-15-mm-927571-346777/</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>Red 530x325x15 mm but polypropylene (not PE)</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>GN-Schneidebrett - mit Füßen - rot - GN 1/1 (530 x 325 mm) - Polyethylen</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-schneidebrett-mit-fuessen-rot-gn-1-1-530-x-325-mm-polyethylen/228313-C</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>Red PE but 20 mm thick (vs 15 mm), with feet; regular price 45.30</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Hendi GN Deckel 1/3 PP, violett</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.allpax.at/product_info.php/info/Hendi-GN-Deckel-1-3-PP-violett.html</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>PP GN 1/3 lid in violet (allergen colour) rather than standard transparent</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront)</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>(6 Stück) CAMBRO SafeTrak Polypropylen-Deckel GN 1/3 - Milchig</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/de-at-eur/6-stueck-cambro-safetrak-polypropylen-deckel-gn-1-3-milchig-30ppcwsc190</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>set of 6</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr"/>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Star</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Polypropylen Deckel GN 1/3</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-star.at/produkt/polypropylendeckelgn13/</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr"/>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>GastroHero Österreich</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Schneider PP GN 1/3 Deckel, einrastend</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastro-hero.at/products/schneider-pp-gn-13-deckel-einrastend-530025</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>Min. qty 8</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Gastrodax</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>WAS GN 89 Deckel 1/3 Polypropylen</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastrodax.de/was-gn-89-deckel-1-3-polypropylen</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>No pack size stated</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Cambro biegsamer Polypropylen Deckel GN 1/3</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/3030@GN-DM714/Cambro-biegsamer-Polypropylen-Deckel-GN-1-3.htm</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="3" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>Flexible soft-seal PP lid</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>GN Deckel GN 89 GN 1/3 weiß (Polypropylen)</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>WAS Germany</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/gn-deckel-gn-89-gn-1-3-weiss-252566</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>GN 89 series is PP (GN 1/1 lid of same series labelled Polypropylen). GN 84 GN 1/3 lid 2.02 (material not stated)</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast GN-Deckel, Polypropylen, für GN 1/3 Behälter</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-gn-deckel-polypropylen-fuer-gn-1-3-behaelter-928338-347853/</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>GN-Deckel - einrastend - GN 1/3 (325 x 176 mm) - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/gn-deckel-einrastend-gn-1-3-325-x-176-mm-polypropylen/530025-C</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>Regular price 3.50</t>
+        </is>
+      </c>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP/PE, wide covered tip</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Araven klare tropffreie Soßenflasche 70cl</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/G16771B@GN-CW113/Araven-klare-tropffreie-So%C3%9Fenflasche-70cl.htm</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="3" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>700 ml PE with drip-free valve and cap; tip width not specified</t>
+        </is>
+      </c>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP/PE, wide covered tip</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Quetschflasche 700 ml Kunststoff gelb Verschlusskappe</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/quetschflasche-700-ml-kunststoff-gelb-verschlusskappe-70-mm-h-240-mm-247040</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>700 ml PE with closure cap over the tip; width of tip not specified</t>
+        </is>
+      </c>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 300x200x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH)</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Hygiplas HDPE kleines Schneidebrett rot 300x225x12mm</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Hygiplas</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gastroladen.at/2310@GN-HC866/Hygiplas-HDPE-kleines-Schneidebrett-rot-300x-225x12mm.htm</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="3" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>Red HDPE, 300x225x12 mm (vs 300x200x20)</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 300x200x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Schneidebrett gelb HDPE 500, 300 mm x 200 mm</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Comas</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/schneidebrett-gelb-hdpe-500-300-mm-x-200-mm-997231</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="3" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>Yellow (red not offered in this size); 20 mm per series size list</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 400x300x100 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Pizzaballenbehälter PP 10 ltr, 400 x 300 x 100 mm</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intergastro.at/pizzaballenbehaelter-pp-10-ltr-400-mm-x-300-mm-h-100-mm-1039856</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="3" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>PP, no lid</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 400x300x100 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Jungheinrich PROFISHOP Austria</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Pizzaballenbehälter aus Polypropylen 400x300x100 mm</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jh-profishop.at/p/stalgast-pizzaballenbehaelter-aus-polypropylen-400x300x100-mm-bxtxh-929479-349076/</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>PP per title, no lid</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 400x300x100 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>shopbuero.com</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Pizzaballenbehälter - 40,0 x 30,0 x 10,0 cm - Inhalt 10,0 l - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>https://shopbuero.com/pizzaballenbehaelter-40-0-x-30-0-x-10-0-cm-inhalt-10-0-l-polypropylen/202175-C</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>PP, no lid; regular price 15.80</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7830,7 +14442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8386,28 +14998,538 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Intergastro (AT shop), shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (Austrian storefront), Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ALLPAX Österreich, GGM Gastro (Austrian storefront), Gastro Star, GastroHero Österreich, Gastrodax, Gastroladen.at (Harotec GmbH), Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP/PE, wide covered tip</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 300x200x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Gastroladen.at (Harotec GmbH), Intergastro (AT shop)</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 400x300x100 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Intergastro (AT shop), Jungheinrich PROFISHOP Austria, shopbuero.com</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>Net price = listed gross / 1.20 (AT standard VAT 20%) when listed incl. VAT; divided by pack size. Only EXACT and CLOSE matches counted.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
